--- a/src/attributions/attributions_saliency_traj_406.xlsx
+++ b/src/attributions/attributions_saliency_traj_406.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.001933500869199634</v>
+        <v>0.002316064899787307</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0121437581256032</v>
+        <v>0.003327398095279932</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001563054509460926</v>
+        <v>0.001394423074088991</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003947262186557055</v>
+        <v>0.0002683543134480715</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008137916447594762</v>
+        <v>0.001851781969889998</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01311733201146126</v>
+        <v>0.005288218148052692</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006663351086899638</v>
+        <v>9.318534284830093e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004580558161251247</v>
+        <v>0.002164598554372787</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001143586996477097</v>
+        <v>0.001186456764116883</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004066075198352337</v>
+        <v>0.002372374758124352</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009003434330224991</v>
+        <v>0.005038661882281303</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007107350393198431</v>
+        <v>0.00155763397924602</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003360959701240063</v>
+        <v>0.000605496228672564</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0006353622302412987</v>
+        <v>7.516122423112392e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0.009728273376822472</v>
+        <v>0.004154067020863295</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0001717007253319025</v>
+        <v>0.001763153122738004</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.001810992602258921</v>
+        <v>0.001790963811799884</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001270586159080267</v>
+        <v>0.0005372326704673469</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0004220464325044304</v>
+        <v>0.001137456391006708</v>
       </c>
       <c r="T4" t="n">
-        <v>0.001314171822741628</v>
+        <v>0.001521611004136503</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008262175833806396</v>
+        <v>0.001627817982807755</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001531231449916959</v>
+        <v>0.000598240178078413</v>
       </c>
       <c r="W4" t="n">
-        <v>0.004239328671246767</v>
+        <v>0.001651424448937178</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0009198036277666688</v>
+        <v>0.001910105696879327</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001206601737067103</v>
+        <v>0.001807714579626918</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001462883781641722</v>
+        <v>0.0009622068027965724</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001465161330997944</v>
+        <v>0.0005599483265541494</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007239601109176874</v>
+        <v>0.0006494944682344794</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.80537094315514e-05</v>
+        <v>0.0006423263112083077</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.001171156531199813</v>
+        <v>0.0009902514284476638</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.001703869318589568</v>
+        <v>0.0008240222232416272</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002525632036849856</v>
+        <v>0.0006734799826517701</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0009908408392220736</v>
+        <v>0.001470573828555644</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.000773691397625953</v>
+        <v>0.0005899161333218217</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.000270762131549418</v>
+        <v>0.002954776166006923</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0005152543308213353</v>
+        <v>0.001391978701576591</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0002871450560633093</v>
+        <v>0.0001863539073383436</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.0006653856253251433</v>
+        <v>0.0003942651383113116</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001690943841822445</v>
+        <v>2.530025085434318e-05</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001512129791080952</v>
+        <v>0.0008541844435967505</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0004735307884402573</v>
+        <v>0.001505937892943621</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.002652952447533607</v>
+        <v>0.001531730405986309</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.001387369004078209</v>
+        <v>0.0007271502981893718</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.001176221296191216</v>
+        <v>0.001548180938698351</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002918095327913761</v>
+        <v>0.0002044108114205301</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0005091011407785118</v>
+        <v>3.359717447892763e-05</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.004550003912299871</v>
+        <v>0.005398395005613565</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.003263306804001331</v>
+        <v>0.001388187287375331</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001470861956477165</v>
+        <v>0.0004383707710076123</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0004496946930885315</v>
+        <v>0.001009550876915455</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.004848449025303125</v>
+        <v>0.003997291438281536</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.003457393730059266</v>
+        <v>1.29511026898399e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.002032236661761999</v>
+        <v>0.0007689903140999377</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.005518716294318438</v>
+        <v>0.0005862210527993739</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.003807293716818094</v>
+        <v>0.002127336105331779</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001904801349155605</v>
+        <v>2.71845783572644e-05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001285966602154076</v>
+        <v>8.502550190314651e-05</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0006067198701202869</v>
+        <v>0.001083313254639506</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.002498139161616564</v>
+        <v>0.001152220065705478</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.004741399083286524</v>
+        <v>0.0007342398166656494</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.003793524112552404</v>
+        <v>0.0006668608402833343</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0007792288670316339</v>
+        <v>0.002967525972053409</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.001796161406673491</v>
+        <v>0.0004831934347748756</v>
       </c>
       <c r="BL4" t="n">
-        <v>7.329834625124931e-05</v>
+        <v>0.0005877057556062937</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0001007564205792733</v>
+        <v>0.001262615900486708</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0002502691349945962</v>
+        <v>1.919665010063909e-06</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0006457462441176176</v>
+        <v>8.330703712999821e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.003621689276769757</v>
+        <v>0.0007065411191433668</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0005527695175260305</v>
+        <v>0.0008504900033585727</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.001249205553904176</v>
+        <v>0.0009479316649958491</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.0005364438402466476</v>
+        <v>0.00071920664049685</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001538660377264023</v>
+        <v>0.0005096280947327614</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.000777867273427546</v>
+        <v>0.0008784681558609009</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003171122167259455</v>
+        <v>0.001053756917826831</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.001361045869998634</v>
+        <v>0.001504850457422435</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0008049097377806902</v>
+        <v>0.001746414229273796</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.00228415010496974</v>
+        <v>0.00115319318138063</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.0001470901188440621</v>
+        <v>0.003276058007031679</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001275198999792337</v>
+        <v>0.001295175403356552</v>
       </c>
       <c r="CB4" t="n">
-        <v>5.988591874483973e-05</v>
+        <v>0.0004448173276614398</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002389666624367237</v>
+        <v>0.0002146251499652863</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0004806956276297569</v>
+        <v>0.0003246419364586473</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001603334327228367</v>
+        <v>0.001250778557732701</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001178249483928084</v>
+        <v>0.0001246569154318422</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0009790000040084124</v>
+        <v>0.0003858652780763805</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0009202992077916861</v>
+        <v>0.0005348835838958621</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002199590904638171</v>
+        <v>0.001073292805813253</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0008968575857579708</v>
+        <v>0.0001408505049766973</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0003086064825765789</v>
+        <v>0.0005840297089889646</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.001716571161523461</v>
+        <v>0.0003371131606400013</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001580981886945665</v>
+        <v>0.0003228083660360426</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.002905781380832195</v>
+        <v>0.002387102227658033</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001540560857392848</v>
+        <v>0.0008371276780962944</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.00166629662271589</v>
+        <v>0.001496953889727592</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.000584126973990351</v>
+        <v>0.0002110092318616807</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.0002981266006827354</v>
+        <v>0.001464844332076609</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.001158563420176506</v>
+        <v>0.001760298036970198</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.0006828588084317744</v>
+        <v>0.001623955322429538</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.001493709627538919</v>
+        <v>0.0005826861597597599</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0002770591818261892</v>
+        <v>0.0005225190543569624</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.001910697785206139</v>
+        <v>0.001001536846160889</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0008639152511022985</v>
+        <v>0.0001703687448753044</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.001198393758386374</v>
+        <v>0.0003677067288663238</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.001246845233254135</v>
+        <v>0.0005906227743253112</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.002332312520593405</v>
+        <v>0.0009264344698749483</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.0003927204816136509</v>
+        <v>9.165395749732852e-05</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.0003406168543733656</v>
+        <v>0.0001989829470403492</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.001722937333397567</v>
+        <v>0.0001289933716179803</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.001245501101948321</v>
+        <v>0.0018408423056826</v>
       </c>
       <c r="DF4" t="n">
-        <v>2.451182808727026e-05</v>
+        <v>9.908189531415701e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0004340670420788229</v>
+        <v>0.0006448414642363787</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.003038076218217611</v>
+        <v>0.0007466537645086646</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.002284939168021083</v>
+        <v>0.001309145009145141</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.005384382791817188</v>
+        <v>0.004264116752892733</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001324106939136982</v>
+        <v>0.0001693818921921775</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.001299469382502139</v>
+        <v>0.001053009647876024</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.005597312469035387</v>
+        <v>0.001072516548447311</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.001176803139969707</v>
+        <v>3.727924195118248e-05</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.0006160518387332559</v>
+        <v>3.565268707461655e-05</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0003483947075437754</v>
+        <v>0.0007366077625192702</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.001387009397149086</v>
+        <v>0.001560466713272035</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0007786048809066415</v>
+        <v>4.472324508242309e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0003943212796002626</v>
+        <v>0.0004998021177016199</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0007955115288496017</v>
+        <v>0.0003418192500248551</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.0006220215000212193</v>
+        <v>7.194439240265638e-05</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0002135928370989859</v>
+        <v>0.0001508896530140191</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.001193274278193712</v>
+        <v>0.0002524999727029353</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0001953759929165244</v>
+        <v>0.001134955557063222</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0005116671090945601</v>
+        <v>0.001231977716088295</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.001817510463297367</v>
+        <v>8.792761946097016e-05</v>
       </c>
       <c r="EA4" t="n">
-        <v>2.820869849529117e-05</v>
+        <v>0.001273681060411036</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.0005513933720067143</v>
+        <v>0.0008460689568892121</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.0009200548520311713</v>
+        <v>5.668133235303685e-05</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0009222732624039054</v>
+        <v>0.002513224957510829</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.001475130440667272</v>
+        <v>0.002289343392476439</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.000424750498495996</v>
+        <v>0.0007482856162823737</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001641942653805017</v>
+        <v>0.0009989344980567694</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0005547618493437767</v>
+        <v>0.0009098147274926305</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.001229396322742105</v>
+        <v>0.001251424429938197</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0008846851997077465</v>
+        <v>0.001265740022063255</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0001420549233444035</v>
+        <v>0.0007263343431986868</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.001636311295442283</v>
+        <v>4.0325026930077e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.000166466023074463</v>
+        <v>0.0004345675115473568</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0005428299773484468</v>
+        <v>0.0006232965388335288</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0005977250402793288</v>
+        <v>0.0004809698439203203</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0008919329266063869</v>
+        <v>0.0004330310330260545</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.00012823028373532</v>
+        <v>0.001248942338861525</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.001538764918223023</v>
+        <v>0.0006002223235554993</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.002744713332504034</v>
+        <v>0.001034563058055937</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.004810320679098368</v>
+        <v>0.002322373911738396</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001535142306238413</v>
+        <v>2.952420618385077e-05</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.001225134241394699</v>
+        <v>0.0005405222764238715</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.002297400962561369</v>
+        <v>0.000371320522390306</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0002640088787302375</v>
+        <v>0.0006652465090155602</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001940917340107262</v>
+        <v>0.001250833156518638</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.000298628699965775</v>
+        <v>0.0002606366178952157</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0008589259814471006</v>
+        <v>0.0004090926086064428</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.001572207780554891</v>
+        <v>0.0009663493256084621</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.001686056610196829</v>
+        <v>0.00108864123467356</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.001295282854698598</v>
+        <v>0.0001445065718144178</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0005195075063966215</v>
+        <v>0.0002919758553616703</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.002352509647607803</v>
+        <v>0.0002552688238210976</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.001129660755395889</v>
+        <v>0.0002827375428751111</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.001343815354630351</v>
+        <v>0.0003745788417290896</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0005134657840244472</v>
+        <v>0.0004153901827521622</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.002688303356990218</v>
+        <v>0.0001206691013067029</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0003854667593259364</v>
+        <v>0.001406562514603138</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.001295232214033604</v>
+        <v>0.001122212270274758</v>
       </c>
       <c r="FM4" t="n">
-        <v>7.803429616615176e-05</v>
+        <v>0.000332357594743371</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0008856490021571517</v>
+        <v>0.0002090114867314696</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.001413339050486684</v>
+        <v>0.002621853724122047</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.0004973222967237234</v>
+        <v>0.001712997211143374</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.001688032643869519</v>
+        <v>6.257655331864953e-05</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.000675459741614759</v>
+        <v>0.000158958020620048</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0005422241520136595</v>
+        <v>0.0005444378475658596</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.003237760625779629</v>
+        <v>0.001801679492928088</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.004470379091799259</v>
+        <v>0.0001074817264452577</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.001042242627590895</v>
+        <v>0.001830239547416568</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0002091119531542063</v>
+        <v>0.002081153448671103</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.001409598742611706</v>
+        <v>0.000928922847378999</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.001948586781509221</v>
+        <v>0.0009939156007021666</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.0008943101856857538</v>
+        <v>0.000720123527571559</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.000870949006639421</v>
+        <v>0.0008799229981377721</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.001955525483936071</v>
+        <v>8.484970749123022e-05</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.003261669538915157</v>
+        <v>0.002483000978827477</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.0004923443193547428</v>
+        <v>0.001428931253030896</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.001749095506966114</v>
+        <v>0.0002972116635646671</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.001004819525405765</v>
+        <v>0.0001860973425209522</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0008146419422701001</v>
+        <v>0.0005178648862056434</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.01002031471580267</v>
+        <v>0.004011079668998718</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03351284936070442</v>
+        <v>0.01643927209079266</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002905758330598474</v>
+        <v>0.001219345023855567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01423442177474499</v>
+        <v>0.01523491460829973</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01246771402657032</v>
+        <v>3.824286977760494e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00893864594399929</v>
+        <v>0.007678478956222534</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0005316099850460887</v>
+        <v>0.006672766525298357</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002981230616569519</v>
+        <v>0.006067105103284121</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00619307067245245</v>
+        <v>0.001621512696146965</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01023528538644314</v>
+        <v>0.006153957918286324</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0249107088893652</v>
+        <v>0.01479475945234299</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005489314207807183</v>
+        <v>0.00586756644770503</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01626911014318466</v>
+        <v>0.02033335715532303</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01959200948476791</v>
+        <v>0.003824974177405238</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01354334875941277</v>
+        <v>0.009151417762041092</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001503556966781616</v>
+        <v>0.008559337817132473</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0006630944553762674</v>
+        <v>0.003485476598143578</v>
       </c>
       <c r="R5" t="n">
-        <v>0.006951282732188702</v>
+        <v>0.001996149076148868</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0003207237459719181</v>
+        <v>0.0004835863073822111</v>
       </c>
       <c r="T5" t="n">
-        <v>0.002477486385032535</v>
+        <v>0.001894614077173173</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001470438088290393</v>
+        <v>0.0003015559632331133</v>
       </c>
       <c r="V5" t="n">
-        <v>0.002147695515304804</v>
+        <v>0.001994837075471878</v>
       </c>
       <c r="W5" t="n">
-        <v>0.007135048508644104</v>
+        <v>0.0007622529519721866</v>
       </c>
       <c r="X5" t="n">
-        <v>0.000815198291093111</v>
+        <v>0.00230193161405623</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.005682711489498615</v>
+        <v>0.001405393937602639</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001679986366070807</v>
+        <v>0.005246209912002087</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.003691526362672448</v>
+        <v>0.0004138879012316465</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.004750910215079784</v>
+        <v>0.001413607154972851</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.005255234893411398</v>
+        <v>0.001969262724742293</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0003295114147476852</v>
+        <v>0.001554136979393661</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.00206784438341856</v>
+        <v>0.0003564523067325354</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.007808451540768147</v>
+        <v>0.001117839943617582</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.004484928213059902</v>
+        <v>0.004590744618326426</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.003258434124290943</v>
+        <v>0.0007081360090523958</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.001188880763947964</v>
+        <v>0.003737743012607098</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0004407758242450655</v>
+        <v>0.0001043019583448768</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0004731870139949024</v>
+        <v>0.001097837346605957</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.003631425090134144</v>
+        <v>0.00387436430901289</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.03040178550873e-05</v>
+        <v>0.003029599320143461</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.001468490809202194</v>
+        <v>0.001559327472932637</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.004345593973994255</v>
+        <v>0.002322586253285408</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.004784356337040663</v>
+        <v>0.001968358643352985</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.003063912503421307</v>
+        <v>0.001737227663397789</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.004235987085849047</v>
+        <v>0.0006756228394806385</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.003173090284690261</v>
+        <v>0.001079584821127355</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.001260075950995088</v>
+        <v>0.0004406058287713677</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.02030766569077969</v>
+        <v>0.006320382468402386</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.001007137470878661</v>
+        <v>0.001139886560849845</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.004432524554431438</v>
+        <v>0.009531199932098389</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.003317815717309713</v>
+        <v>0.01082545891404152</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.006671127863228321</v>
+        <v>0.004943401552736759</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0091018071398139</v>
+        <v>0.0003044857294298708</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.007835415191948414</v>
+        <v>0.001845074584707618</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0005856407806277275</v>
+        <v>0.003375159343704581</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0004198136739432812</v>
+        <v>0.003253158647567034</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.007246105931699276</v>
+        <v>0.002296092920005322</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.007039925549179316</v>
+        <v>0.002879631705582142</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.001252347370609641</v>
+        <v>0.001427435548976064</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.01443800516426563</v>
+        <v>0.00487613258883357</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.006146852858364582</v>
+        <v>0.003202612046152353</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.005876594688743353</v>
+        <v>0.001990241464227438</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.002595547121018171</v>
+        <v>0.005711299832910299</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.007212919648736715</v>
+        <v>0.002359318314120173</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.001919939881190658</v>
+        <v>0.001523599261417985</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.001651159022003412</v>
+        <v>0.003415841143578291</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.003718716558068991</v>
+        <v>0.0004765046178363264</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.004365505650639534</v>
+        <v>0.001642950344830751</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.003216699697077274</v>
+        <v>0.002583177294582129</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.002640165854245424</v>
+        <v>0.001714175567030907</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.003476834390312433</v>
+        <v>0.0007337937713600695</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.001104662660509348</v>
+        <v>0.0008113118237815797</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.00184880499728024</v>
+        <v>0.001492489827796817</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.362292096018791e-06</v>
+        <v>0.0004014171427115798</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.01057400275021791</v>
+        <v>0.005067096557468176</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.003233044408261776</v>
+        <v>0.001873099477961659</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.005280195735394955</v>
+        <v>0.007954820990562439</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.004450939130038023</v>
+        <v>0.0004820432513952255</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.809892248478718e-05</v>
+        <v>0.002052571624517441</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.003500635735690594</v>
+        <v>0.001692134654149413</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.006112292874604464</v>
+        <v>0.002419963944703341</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.003543478203937411</v>
+        <v>0.001143370405770838</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.001751992851495743</v>
+        <v>0.001436443533748388</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.005721278954297304</v>
+        <v>0.004500864073634148</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.00269233575090766</v>
+        <v>9.832403156906366e-05</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.002432993613183498</v>
+        <v>0.00566862802952528</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001216288888826966</v>
+        <v>0.00077452277764678</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.001019829651340842</v>
+        <v>0.0005317218601703644</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.002079734113067389</v>
+        <v>0.000199298927327618</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0008212203974835575</v>
+        <v>0.0004994797054678202</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0003693534526973963</v>
+        <v>0.0004731237422674894</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.006621191743761301</v>
+        <v>4.188728053122759e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.001849903725087643</v>
+        <v>0.0004554764600470662</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.000682282610796392</v>
+        <v>0.006053430028259754</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.00176281644962728</v>
+        <v>0.009416477754712105</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.009393889456987381</v>
+        <v>0.0006326321745291352</v>
       </c>
       <c r="CR5" t="n">
-        <v>3.041932359337807e-05</v>
+        <v>5.750512355007231e-05</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.006032145582139492</v>
+        <v>0.001904991338960826</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.007135047577321529</v>
+        <v>0.0042001330293715</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.0003836680552922189</v>
+        <v>0.0007134298793971539</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.002154065296053886</v>
+        <v>0.001314490335062146</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.004938811529427767</v>
+        <v>0.004569641314446926</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.003279200987890363</v>
+        <v>0.0007697223336435854</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.002378038829192519</v>
+        <v>0.005851325578987598</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.001713126199319959</v>
+        <v>3.933873813366517e-05</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0006899292347952724</v>
+        <v>0.001105333329178393</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.002632114803418517</v>
+        <v>0.0004661871353164315</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0003625838435254991</v>
+        <v>0.000168803075212054</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0007553681498393416</v>
+        <v>0.0001130410237237811</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.0003284002305008471</v>
+        <v>0.003358018584549427</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0008150287321768701</v>
+        <v>0.004648897796869278</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.00216122530400753</v>
+        <v>0.00561866769567132</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.006949787959456444</v>
+        <v>0.007576181553304195</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0008580487919971347</v>
+        <v>0.003615295980125666</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.001731515163555741</v>
+        <v>0.00707691628485918</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.002659515012055635</v>
+        <v>9.759636304806918e-05</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.00382938189432025</v>
+        <v>0.006341888569295406</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0004435289883986115</v>
+        <v>0.0003555710427463055</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.002324171364307404</v>
+        <v>0.00186367891728878</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.004457294940948486</v>
+        <v>0.002468156395480037</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001967081567272544</v>
+        <v>0.0003191512078046799</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.002669396577402949</v>
+        <v>0.003891010070219636</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0005598963471129537</v>
+        <v>0.000539775937795639</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.002725443104282022</v>
+        <v>0.001233465736731887</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0005700676701962948</v>
+        <v>0.00380065618082881</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.002490344224497676</v>
+        <v>0.001704683993011713</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.002517409389838576</v>
+        <v>0.005508203525096178</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.001200810540467501</v>
+        <v>0.001150715979747474</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.002507942961528897</v>
+        <v>0.001071602571755648</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.003168239491060376</v>
+        <v>0.001497507095336914</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.00321119069121778</v>
+        <v>0.002170325024053454</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.003850651439279318</v>
+        <v>0.0003840325807686895</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.00247721909545362</v>
+        <v>0.003083417192101479</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0007948047714307904</v>
+        <v>0.0003782102721743286</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.00622475054115057</v>
+        <v>0.009236485697329044</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.000320213584927842</v>
+        <v>0.005441101733595133</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.002562984358519316</v>
+        <v>0.004485671874135733</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.002816115971654654</v>
+        <v>0.002616797341033816</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.002319614170119166</v>
+        <v>0.002130028326064348</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.000522912829183042</v>
+        <v>0.005723045207560062</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.004249795340001583</v>
+        <v>0.0005876558134332299</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0007888915133662522</v>
+        <v>0.0001982185494853184</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.003321003401651978</v>
+        <v>0.000360543344868347</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0009530609822832048</v>
+        <v>0.001383971306495368</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0002048518799711019</v>
+        <v>0.0009969086386263371</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.001595842069946229</v>
+        <v>0.0004056391189806163</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.005930490791797638</v>
+        <v>0.005796650890260935</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.002878618892282248</v>
+        <v>0.0002255350700579584</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.003096852684393525</v>
+        <v>0.001531737856566906</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.005731455981731415</v>
+        <v>0.0005390582955442369</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.007334918715059757</v>
+        <v>0.00293167307972908</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.004985871724784374</v>
+        <v>0.00261268112808466</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.005134608130902052</v>
+        <v>0.0009436313412152231</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001418197527527809</v>
+        <v>0.003378148889169097</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.001137927058152854</v>
+        <v>0.001156999613158405</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.004495388828217983</v>
+        <v>0.004326409660279751</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.00210056989453733</v>
+        <v>0.0001459281775169075</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.002770221792161465</v>
+        <v>0.006853762082755566</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.002016307786107063</v>
+        <v>0.0002777008921839297</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.001810337067581713</v>
+        <v>0.0002505003358237445</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.002950435504317284</v>
+        <v>0.0005930911283940077</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.001013552537187934</v>
+        <v>0.0007830290705896914</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.001632108469493687</v>
+        <v>0.0004952191957272589</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0003856768016703427</v>
+        <v>0.0005945523735135794</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0007692491635680199</v>
+        <v>0.002507462631911039</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.001515736803412437</v>
+        <v>0.0009465297916904092</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.005339121446013451</v>
+        <v>0.003883214201778173</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0001006578677333891</v>
+        <v>0.000315285666147247</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0006256374763324857</v>
+        <v>0.0003549177199602127</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.004782274831086397</v>
+        <v>0.002496822271496058</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.001025935518555343</v>
+        <v>0.002989658154547215</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0005075165536254644</v>
+        <v>0.0006110848044045269</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.006599685177206993</v>
+        <v>0.003320336807519197</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.004390784073621035</v>
+        <v>0.007243144325911999</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.0005867808358743787</v>
+        <v>0.003551197005435824</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.001950679230503738</v>
+        <v>0.006214993074536324</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.004926054272800684</v>
+        <v>0.0001804330386221409</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0001423415669705719</v>
+        <v>0.006237163208425045</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.003784287255257368</v>
+        <v>0.0002108211629092693</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.002431687898933887</v>
+        <v>0.001067463308572769</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.001484627486206591</v>
+        <v>0.008947869762778282</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.004962573759257793</v>
+        <v>0.001660864800214767</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0007410679245367646</v>
+        <v>0.000235671061091125</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.0006365833687596023</v>
+        <v>0.0001482612424297258</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.0006357087986543775</v>
+        <v>0.004961199127137661</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.00109201914165169</v>
+        <v>0.001529320608824492</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.004218106158077717</v>
+        <v>0.0009032902307808399</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.009573505260050297</v>
+        <v>0.003071460407227278</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.005034937988966703</v>
+        <v>0.001054487540386617</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.002022858709096909</v>
+        <v>0.001623441115953028</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0003539921308401972</v>
+        <v>1.025100004881097e-06</v>
       </c>
       <c r="B6" t="n">
-        <v>7.924320379970595e-05</v>
+        <v>5.851101718690188e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0001981580135179684</v>
+        <v>1.098883672057127e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002924668369814754</v>
+        <v>2.557649452228361e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001584949204698205</v>
+        <v>1.099024530049064e-06</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001131581608206034</v>
+        <v>8.763752248341916e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008794215973466635</v>
+        <v>9.395972710990463e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001073442326742224</v>
+        <v>3.776181074499618e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001160412328317761</v>
+        <v>5.7667335795486e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000430714018875733</v>
+        <v>8.419476671406301e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>9.795243386179209e-05</v>
+        <v>1.5072803307703e-06</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001548978762002662</v>
+        <v>1.056575911206892e-06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0003719160449691117</v>
+        <v>1.92115891195499e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001276569440960884</v>
+        <v>7.810939450791921e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>0.001175866229459643</v>
+        <v>6.961822123230377e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0005649465601891279</v>
+        <v>1.327211521129357e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.317143121734262e-05</v>
+        <v>4.129930175622576e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000645569059997797</v>
+        <v>1.55852006855639e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001283238962059841</v>
+        <v>3.539984163580812e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0004710287612397224</v>
+        <v>7.37100663172896e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>2.452915941830724e-05</v>
+        <v>2.354199182263983e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>9.749492164701223e-06</v>
+        <v>7.928246077426593e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0008593617822043598</v>
+        <v>1.0831531653821e-06</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0002816266496665776</v>
+        <v>7.818448466423433e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001256153627764434</v>
+        <v>5.335620016921894e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0002883425622712821</v>
+        <v>3.889324773354019e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0001214190706377849</v>
+        <v>2.990771008626325e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.951117832912132e-05</v>
+        <v>1.180484616725153e-07</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0002775954490061849</v>
+        <v>3.465261784185714e-07</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0002072369097732008</v>
+        <v>5.866908168172813e-07</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.000642299884930253</v>
+        <v>7.617243227286963e-07</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.001211467199027538</v>
+        <v>2.765711997199105e-07</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0003252593451179564</v>
+        <v>9.72008891153564e-08</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0007173398043960333</v>
+        <v>1.996023968331428e-08</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.000303546607028693</v>
+        <v>5.805147225146357e-07</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.066089993808419e-05</v>
+        <v>1.513713243639359e-08</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0001556912175146863</v>
+        <v>2.298464636396602e-07</v>
       </c>
       <c r="AL6" t="n">
-        <v>9.199736086884513e-05</v>
+        <v>4.641947271011304e-08</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.684169183135964e-05</v>
+        <v>1.211149509572351e-07</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0005242459592409432</v>
+        <v>6.480442493739247e-07</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0003281938843429089</v>
+        <v>4.95763174512831e-07</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0001846776285674423</v>
+        <v>3.920424944681145e-07</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0003283318947069347</v>
+        <v>4.61805882423505e-09</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.000203619449166581</v>
+        <v>8.863724332286438e-08</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.303103534970433e-06</v>
+        <v>1.713290487259655e-08</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0002763960801530629</v>
+        <v>9.357422925404535e-08</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.0002615317353047431</v>
+        <v>1.954368599399459e-06</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.000136886301334016</v>
+        <v>5.745617954744375e-07</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.001160496147349477</v>
+        <v>1.098078286076998e-07</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.001503078383393586</v>
+        <v>3.037259546090354e-07</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0003711151948664337</v>
+        <v>3.866707629640587e-07</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.001731519005261362</v>
+        <v>5.294247102938243e-07</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.001369730685837567</v>
+        <v>8.211188742279774e-07</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0004976731142960489</v>
+        <v>2.004787518217199e-07</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.000563546025659889</v>
+        <v>6.907506531206309e-07</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0001874322188086808</v>
+        <v>4.920945571029733e-07</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.600709169404581e-05</v>
+        <v>1.304036914007156e-07</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0001121120876632631</v>
+        <v>7.980206646607257e-07</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0006485026096925139</v>
+        <v>8.845040611049626e-08</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0006897883140482008</v>
+        <v>3.591672737002227e-08</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0004058523918502033</v>
+        <v>3.363560949765088e-07</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0001099597720894963</v>
+        <v>1.228618771165202e-06</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.60324517916888e-05</v>
+        <v>3.095259728524979e-07</v>
       </c>
       <c r="BL6" t="n">
-        <v>8.787596016190946e-05</v>
+        <v>2.638644502894749e-07</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0001124173213611357</v>
+        <v>5.260612283564114e-07</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.000339721271302551</v>
+        <v>5.778149514412689e-08</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.001170167233794928</v>
+        <v>1.280413215454246e-07</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0001810860994737595</v>
+        <v>3.635655900779966e-07</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0002069339971058071</v>
+        <v>1.350257008425615e-07</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0006193573353812099</v>
+        <v>4.966966571373632e-08</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.0005869599990546703</v>
+        <v>1.118548169642963e-07</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0006388467154465616</v>
+        <v>2.11168298847042e-07</v>
       </c>
       <c r="BU6" t="n">
-        <v>9.000021236715838e-05</v>
+        <v>2.1126120941517e-07</v>
       </c>
       <c r="BV6" t="n">
-        <v>1.747450005495921e-05</v>
+        <v>3.057715787235793e-07</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0001078173299902119</v>
+        <v>4.934246362608974e-07</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0004128774162381887</v>
+        <v>1.245323574039503e-06</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0007667234749533236</v>
+        <v>3.946792617171013e-07</v>
       </c>
       <c r="BZ6" t="n">
-        <v>5.253209747024812e-05</v>
+        <v>8.565821190131828e-07</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.000773111532907933</v>
+        <v>2.458105541336408e-07</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0005542041617445648</v>
+        <v>2.201941669000007e-07</v>
       </c>
       <c r="CC6" t="n">
-        <v>7.041680510155857e-05</v>
+        <v>1.805145473099401e-07</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.720592187368311e-05</v>
+        <v>3.761875291274919e-07</v>
       </c>
       <c r="CE6" t="n">
-        <v>5.347289334167726e-05</v>
+        <v>2.389660949120298e-07</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0001204439031425864</v>
+        <v>5.605789255014315e-08</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0001253805821761489</v>
+        <v>4.945225384744845e-08</v>
       </c>
       <c r="CH6" t="n">
-        <v>2.682437479961663e-05</v>
+        <v>8.600395062785537e-08</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.354326352360658e-05</v>
+        <v>1.255524608723135e-07</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.000218333094380796</v>
+        <v>2.608306317597453e-07</v>
       </c>
       <c r="CK6" t="n">
-        <v>5.124003655510023e-05</v>
+        <v>2.144020072591957e-07</v>
       </c>
       <c r="CL6" t="n">
-        <v>6.50696165394038e-05</v>
+        <v>2.524224953504017e-07</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0001305749756284058</v>
+        <v>3.184892705121456e-07</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0003970080288127065</v>
+        <v>3.769179386381438e-07</v>
       </c>
       <c r="CO6" t="n">
-        <v>3.169458796037361e-05</v>
+        <v>2.093902651267854e-07</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0001045721292030066</v>
+        <v>1.548952184293739e-07</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0006796178640797734</v>
+        <v>2.400475693775661e-07</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0004641228006221354</v>
+        <v>1.148269319628525e-07</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.0005037590744905174</v>
+        <v>8.895883070181299e-07</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0006375725497491658</v>
+        <v>5.062014452050789e-07</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0006310832104645669</v>
+        <v>7.888360187280341e-08</v>
       </c>
       <c r="CV6" t="n">
-        <v>6.069729715818539e-05</v>
+        <v>4.642026851797709e-07</v>
       </c>
       <c r="CW6" t="n">
-        <v>7.122533861547709e-05</v>
+        <v>1.410487868724886e-07</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.0001061085276887752</v>
+        <v>1.252898016446125e-07</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.000132631219457835</v>
+        <v>1.883677214209456e-08</v>
       </c>
       <c r="CZ6" t="n">
-        <v>3.164169902447611e-05</v>
+        <v>1.452068829621567e-07</v>
       </c>
       <c r="DA6" t="n">
-        <v>6.105200736783445e-05</v>
+        <v>4.102238193581798e-08</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0001199769467348233</v>
+        <v>1.787118293350431e-07</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.124110324075446e-05</v>
+        <v>1.588855838008385e-07</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.0001190017210319638</v>
+        <v>2.483815535470058e-07</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0002936339005827904</v>
+        <v>4.877175001638534e-07</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0007515963516198099</v>
+        <v>6.620742851737305e-07</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.358841786393896e-05</v>
+        <v>2.216056742554429e-07</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0005301237688399851</v>
+        <v>3.611584986629168e-07</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0006640327628701925</v>
+        <v>8.923484529077541e-07</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0006545958458445966</v>
+        <v>6.640519814027357e-07</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0001764079352142289</v>
+        <v>3.586688990253606e-07</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0004199628601782024</v>
+        <v>4.52665659622653e-07</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.00121723476331681</v>
+        <v>1.343030788802935e-07</v>
       </c>
       <c r="DN6" t="n">
-        <v>6.682617095066234e-05</v>
+        <v>1.473956956488109e-07</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0001352447579847649</v>
+        <v>7.383847133723975e-08</v>
       </c>
       <c r="DP6" t="n">
-        <v>5.923808930674568e-05</v>
+        <v>5.740733399761666e-07</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0004179358074907213</v>
+        <v>8.30637588933314e-07</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0007481194916181266</v>
+        <v>4.022493271804706e-07</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.0002049757749773562</v>
+        <v>5.332396995072486e-07</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0002479542163200676</v>
+        <v>7.233510501691853e-08</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0002535276871640235</v>
+        <v>1.97358772879852e-07</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.0007385030621662736</v>
+        <v>2.57715811358139e-07</v>
       </c>
       <c r="DW6" t="n">
-        <v>2.758077607722953e-05</v>
+        <v>6.781532420063741e-07</v>
       </c>
       <c r="DX6" t="n">
-        <v>7.107562851160765e-05</v>
+        <v>2.491732118414802e-07</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0001637249806663021</v>
+        <v>9.489522767580638e-07</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0006217491463758051</v>
+        <v>2.242786081296799e-07</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0006047983188182116</v>
+        <v>5.618900331683108e-07</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0001031413485179655</v>
+        <v>2.607691840239568e-07</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.472066964604892e-05</v>
+        <v>4.014445096345298e-07</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0006586184026673436</v>
+        <v>7.017369512141158e-07</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0001609071041457355</v>
+        <v>7.224924161164381e-07</v>
       </c>
       <c r="EF6" t="n">
-        <v>8.39071290101856e-05</v>
+        <v>4.943819931213511e-07</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.0001410820696037263</v>
+        <v>4.767541383898788e-07</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0001488127891207114</v>
+        <v>1.575987198521034e-07</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.001137679093517363</v>
+        <v>2.767214368759596e-07</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0001000181073322892</v>
+        <v>4.376038305053953e-07</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0003593044239096344</v>
+        <v>6.118467865690036e-08</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0005037258379161358</v>
+        <v>1.241708957877563e-10</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.0002558919659350067</v>
+        <v>1.34125514250627e-07</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0001302838645642623</v>
+        <v>6.596402499781107e-07</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0001416390587110072</v>
+        <v>3.730764888132398e-07</v>
       </c>
       <c r="EP6" t="n">
-        <v>4.602418630383909e-05</v>
+        <v>5.75003866742918e-08</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0001473964512115344</v>
+        <v>4.712355234914867e-07</v>
       </c>
       <c r="ER6" t="n">
-        <v>1.550713750475552e-05</v>
+        <v>1.968225831205928e-07</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.000410886510508135</v>
+        <v>1.729501803993116e-07</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0005694126011803746</v>
+        <v>5.823719675390748e-07</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0004928906564600766</v>
+        <v>2.463258397256141e-08</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.0002916338853538036</v>
+        <v>1.093692532094792e-07</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0001758428115863353</v>
+        <v>6.065530300247701e-08</v>
       </c>
       <c r="EX6" t="n">
-        <v>4.489795173867606e-05</v>
+        <v>5.37223286301014e-07</v>
       </c>
       <c r="EY6" t="n">
-        <v>7.717914559179917e-05</v>
+        <v>2.400077505626541e-07</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0001654277584748343</v>
+        <v>2.013566415826062e-07</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0001534490729682148</v>
+        <v>8.619871039172722e-08</v>
       </c>
       <c r="FB6" t="n">
-        <v>2.843371476046741e-05</v>
+        <v>2.184972913710226e-07</v>
       </c>
       <c r="FC6" t="n">
-        <v>2.72503948508529e-05</v>
+        <v>1.765055230862345e-07</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0002022124535869807</v>
+        <v>1.733985754981404e-07</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.0001144492271123454</v>
+        <v>6.198630586595755e-08</v>
       </c>
       <c r="FF6" t="n">
-        <v>2.569570824562106e-06</v>
+        <v>1.788905876765057e-07</v>
       </c>
       <c r="FG6" t="n">
-        <v>1.159023031505058e-05</v>
+        <v>8.224549787883007e-07</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0001389244571328163</v>
+        <v>1.000894656044693e-08</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0002430641616228968</v>
+        <v>2.839648232111358e-07</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0007799987215548754</v>
+        <v>1.064355217295088e-07</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0002459300449118018</v>
+        <v>9.845466593105812e-07</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0005509482580237091</v>
+        <v>1.416689343614053e-08</v>
       </c>
       <c r="FM6" t="n">
-        <v>5.491907359100878e-05</v>
+        <v>1.961826541219125e-07</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0001338417205261067</v>
+        <v>2.172964599367333e-07</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.000584970461204648</v>
+        <v>8.103248774204985e-07</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0004459458577912301</v>
+        <v>5.184323299545213e-07</v>
       </c>
       <c r="FQ6" t="n">
-        <v>6.120496982475743e-05</v>
+        <v>8.427042530456674e-07</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0002114722301485017</v>
+        <v>5.926274297962664e-07</v>
       </c>
       <c r="FS6" t="n">
-        <v>2.845044946298003e-05</v>
+        <v>3.566628095086344e-07</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001501989085227251</v>
+        <v>2.171537516915123e-06</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.001184701803140342</v>
+        <v>7.248939937198884e-08</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0007317680865526199</v>
+        <v>7.920049824861053e-07</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0005832696915604174</v>
+        <v>8.007866654224927e-07</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.0002167492784792557</v>
+        <v>5.987450890643231e-07</v>
       </c>
       <c r="FY6" t="n">
-        <v>7.564826228190213e-05</v>
+        <v>5.104603673089514e-08</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.0001304176112171263</v>
+        <v>4.095214762855903e-07</v>
       </c>
       <c r="GA6" t="n">
-        <v>8.570723730372265e-05</v>
+        <v>6.209007210600248e-07</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0005201405147090554</v>
+        <v>3.036062423689145e-07</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0005867000436410308</v>
+        <v>3.346748940202815e-07</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0007323318859562278</v>
+        <v>2.578413216269837e-08</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0008123161387629807</v>
+        <v>2.124740738906894e-08</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0005760759231634438</v>
+        <v>4.39382858985482e-07</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.001211042981594801</v>
+        <v>3.534869392751716e-07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8.924128451326396e-06</v>
+        <v>3.833975373507617e-14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.326563662791159e-05</v>
+        <v>9.3370393339752e-14</v>
       </c>
       <c r="C7" t="n">
-        <v>6.513437256217003e-07</v>
+        <v>4.030764166450956e-13</v>
       </c>
       <c r="D7" t="n">
-        <v>7.191827990027377e-06</v>
+        <v>3.150840591041593e-13</v>
       </c>
       <c r="E7" t="n">
-        <v>2.774702807073481e-06</v>
+        <v>6.966474651922544e-14</v>
       </c>
       <c r="F7" t="n">
-        <v>7.385010121652158e-06</v>
+        <v>7.193575162628418e-13</v>
       </c>
       <c r="G7" t="n">
-        <v>6.158357450658514e-07</v>
+        <v>1.104437721832774e-13</v>
       </c>
       <c r="H7" t="n">
-        <v>2.064027285086922e-06</v>
+        <v>2.62811623050023e-14</v>
       </c>
       <c r="I7" t="n">
-        <v>1.27710964079597e-05</v>
+        <v>5.269256168546899e-13</v>
       </c>
       <c r="J7" t="n">
-        <v>6.74525608701515e-06</v>
+        <v>2.056644446218024e-14</v>
       </c>
       <c r="K7" t="n">
-        <v>1.070175130735151e-05</v>
+        <v>7.621212688713186e-13</v>
       </c>
       <c r="L7" t="n">
-        <v>1.033225885294087e-06</v>
+        <v>3.888420347427507e-13</v>
       </c>
       <c r="M7" t="n">
-        <v>1.316397265327396e-05</v>
+        <v>6.31404542365821e-13</v>
       </c>
       <c r="N7" t="n">
-        <v>9.133391358773224e-06</v>
+        <v>5.145682125296154e-14</v>
       </c>
       <c r="O7" t="n">
-        <v>3.118419044767506e-06</v>
+        <v>6.484630540870562e-13</v>
       </c>
       <c r="P7" t="n">
-        <v>4.23805249738507e-06</v>
+        <v>2.773073112284641e-13</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.938710622402141e-06</v>
+        <v>2.684011324825819e-13</v>
       </c>
       <c r="R7" t="n">
-        <v>9.674144166638143e-06</v>
+        <v>2.887703097476102e-13</v>
       </c>
       <c r="S7" t="n">
-        <v>9.983866675611353e-07</v>
+        <v>1.483320980150485e-13</v>
       </c>
       <c r="T7" t="n">
-        <v>1.394119976794173e-06</v>
+        <v>3.433642259409453e-13</v>
       </c>
       <c r="U7" t="n">
-        <v>1.07445293906494e-06</v>
+        <v>1.59662620581244e-13</v>
       </c>
       <c r="V7" t="n">
-        <v>3.019094492628938e-06</v>
+        <v>3.534735980477433e-13</v>
       </c>
       <c r="W7" t="n">
-        <v>6.311062861641403e-06</v>
+        <v>7.050125457389034e-13</v>
       </c>
       <c r="X7" t="n">
-        <v>1.052930201694835e-06</v>
+        <v>3.19678745280827e-13</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.299443728290498e-08</v>
+        <v>1.094315203774635e-13</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.437400214854279e-06</v>
+        <v>1.265882201579444e-13</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.491845580403606e-07</v>
+        <v>1.220019229955863e-13</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.314807261427632e-07</v>
+        <v>1.827443361565595e-13</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.192625510768266e-06</v>
+        <v>2.520725327689183e-14</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.744135938177351e-06</v>
+        <v>2.320471560127851e-13</v>
       </c>
       <c r="AE7" t="n">
-        <v>4.465598067326937e-06</v>
+        <v>3.724123873866114e-13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.574009900195961e-07</v>
+        <v>5.248321173273104e-15</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.467638741014525e-06</v>
+        <v>2.688820574612422e-13</v>
       </c>
       <c r="AH7" t="n">
-        <v>5.901133022234717e-07</v>
+        <v>1.073633369708116e-13</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.644453050175798e-06</v>
+        <v>4.08816101631071e-13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4.366726443549851e-06</v>
+        <v>9.402534631962334e-14</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.414332473359536e-06</v>
+        <v>1.87672631341701e-13</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.470703637096449e-06</v>
+        <v>1.973014443880719e-13</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.424469360244984e-06</v>
+        <v>9.955791480933604e-14</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.006151119843707e-07</v>
+        <v>4.100468879372765e-13</v>
       </c>
       <c r="AO7" t="n">
-        <v>3.91970115742879e-06</v>
+        <v>2.902266643158014e-13</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.316140115814051e-06</v>
+        <v>8.905260562167353e-15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.765360361285275e-06</v>
+        <v>4.072959959751377e-14</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.033919478591997e-06</v>
+        <v>1.59387694015356e-13</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.744280211823934e-06</v>
+        <v>1.639572131490949e-13</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.256989652480115e-07</v>
+        <v>4.398043073391283e-14</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.993793193832971e-05</v>
+        <v>9.20529819904703e-13</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.636248271097429e-06</v>
+        <v>1.305257307402871e-13</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.378921519470168e-06</v>
+        <v>1.69949923817074e-13</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.187605266750325e-05</v>
+        <v>1.831701023496946e-13</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.560086148965638e-06</v>
+        <v>1.083639742608528e-15</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.026311555411667e-06</v>
+        <v>9.872917777374243e-14</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.388853317825124e-06</v>
+        <v>2.337967601635793e-13</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.269473604130326e-07</v>
+        <v>1.718662104993607e-13</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.764313416671939e-06</v>
+        <v>2.037755679256889e-13</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.019145075697452e-07</v>
+        <v>2.235051472241137e-13</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.122368075812119e-06</v>
+        <v>6.00351677550702e-14</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.485141173267039e-06</v>
+        <v>3.016229844013396e-13</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.858233417806332e-06</v>
+        <v>1.290156539544493e-13</v>
       </c>
       <c r="BH7" t="n">
-        <v>2.257422238471918e-06</v>
+        <v>3.411609644961289e-13</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.060359409166267e-06</v>
+        <v>2.522695051986046e-13</v>
       </c>
       <c r="BJ7" t="n">
-        <v>3.085800244662096e-06</v>
+        <v>2.605862303283607e-13</v>
       </c>
       <c r="BK7" t="n">
-        <v>9.689743819762953e-06</v>
+        <v>1.577930494600643e-13</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.24674829748983e-06</v>
+        <v>2.834203954426434e-13</v>
       </c>
       <c r="BM7" t="n">
-        <v>3.033621396753006e-06</v>
+        <v>3.065248250534724e-13</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.934809799626237e-06</v>
+        <v>5.298402843312462e-15</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.612980551930377e-06</v>
+        <v>4.174183785080054e-14</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.223749586642953e-05</v>
+        <v>3.523994247453532e-13</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.772801851984696e-06</v>
+        <v>2.974404847855966e-13</v>
       </c>
       <c r="BR7" t="n">
-        <v>1.171042185887927e-06</v>
+        <v>4.055311587838201e-13</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.053564801622997e-06</v>
+        <v>8.736276811563762e-14</v>
       </c>
       <c r="BT7" t="n">
-        <v>2.515912456146907e-06</v>
+        <v>5.23754081554681e-14</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.383254801927251e-07</v>
+        <v>1.423901686663231e-14</v>
       </c>
       <c r="BV7" t="n">
-        <v>9.475135811953805e-06</v>
+        <v>2.05934255108689e-13</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.867208993644454e-06</v>
+        <v>2.751515378388025e-13</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.84423811333545e-06</v>
+        <v>4.272369675921428e-13</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.468465936544817e-06</v>
+        <v>3.640661448527094e-13</v>
       </c>
       <c r="BZ7" t="n">
-        <v>5.200113264436368e-07</v>
+        <v>4.106143322493011e-13</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.236580353899626e-07</v>
+        <v>4.006892745118257e-14</v>
       </c>
       <c r="CB7" t="n">
-        <v>1.774814222699206e-06</v>
+        <v>2.607272850310011e-13</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.680071464870707e-07</v>
+        <v>3.156720219422982e-13</v>
       </c>
       <c r="CD7" t="n">
-        <v>1.115551867769682e-06</v>
+        <v>9.647026287615962e-14</v>
       </c>
       <c r="CE7" t="n">
-        <v>3.702016783790896e-06</v>
+        <v>1.440363009663466e-15</v>
       </c>
       <c r="CF7" t="n">
-        <v>5.373611315917515e-07</v>
+        <v>7.367352306561839e-14</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.14734063774813e-06</v>
+        <v>1.58354855920792e-13</v>
       </c>
       <c r="CH7" t="n">
-        <v>9.027450005305582e-07</v>
+        <v>3.512715427778437e-14</v>
       </c>
       <c r="CI7" t="n">
-        <v>7.373470793936576e-07</v>
+        <v>1.307771030139779e-13</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.260517592527322e-07</v>
+        <v>6.5554935882884e-14</v>
       </c>
       <c r="CK7" t="n">
-        <v>5.95224889821111e-07</v>
+        <v>3.492980915360128e-14</v>
       </c>
       <c r="CL7" t="n">
-        <v>3.141029310427257e-06</v>
+        <v>1.502670871848105e-13</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.602155291242525e-06</v>
+        <v>1.235551374753618e-13</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.551957550167572e-06</v>
+        <v>3.88372277046467e-13</v>
       </c>
       <c r="CO7" t="n">
-        <v>8.350868796469513e-08</v>
+        <v>1.7133939666375e-13</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.455038955100463e-06</v>
+        <v>1.235899674701529e-13</v>
       </c>
       <c r="CQ7" t="n">
-        <v>8.401171726291068e-06</v>
+        <v>1.833803562559938e-13</v>
       </c>
       <c r="CR7" t="n">
-        <v>4.205772711429745e-06</v>
+        <v>1.037639754935399e-14</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.486397988832323e-06</v>
+        <v>8.79480814347175e-14</v>
       </c>
       <c r="CT7" t="n">
-        <v>4.361712399258977e-06</v>
+        <v>1.27040522199251e-13</v>
       </c>
       <c r="CU7" t="n">
-        <v>9.566814469508245e-07</v>
+        <v>2.27241240147863e-13</v>
       </c>
       <c r="CV7" t="n">
-        <v>8.508423547937127e-07</v>
+        <v>1.331858749805889e-13</v>
       </c>
       <c r="CW7" t="n">
-        <v>3.553092483343789e-06</v>
+        <v>8.906398974448462e-15</v>
       </c>
       <c r="CX7" t="n">
-        <v>4.020463109100092e-07</v>
+        <v>5.195915922452839e-14</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.982199819394737e-06</v>
+        <v>1.724005595400702e-13</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.421879119334335e-06</v>
+        <v>5.649443112214388e-14</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.754221029022119e-08</v>
+        <v>1.180364806547748e-13</v>
       </c>
       <c r="DB7" t="n">
-        <v>3.298415549579659e-07</v>
+        <v>3.848944139751495e-14</v>
       </c>
       <c r="DC7" t="n">
-        <v>4.859574005422473e-07</v>
+        <v>4.930451731025194e-15</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.382603042860865e-06</v>
+        <v>1.311223536432787e-13</v>
       </c>
       <c r="DE7" t="n">
-        <v>3.64480251846544e-06</v>
+        <v>1.047289357558427e-13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.412688743585022e-05</v>
+        <v>1.439366475401022e-13</v>
       </c>
       <c r="DG7" t="n">
-        <v>3.96856376028154e-06</v>
+        <v>1.754408386145725e-13</v>
       </c>
       <c r="DH7" t="n">
-        <v>1.020134732243605e-05</v>
+        <v>1.249289164955911e-13</v>
       </c>
       <c r="DI7" t="n">
-        <v>4.671911938203266e-06</v>
+        <v>9.266563482258211e-14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>4.862698915530927e-06</v>
+        <v>1.957654416177845e-13</v>
       </c>
       <c r="DK7" t="n">
-        <v>2.119169948855415e-06</v>
+        <v>1.014049209728009e-13</v>
       </c>
       <c r="DL7" t="n">
-        <v>8.727956810616888e-06</v>
+        <v>1.443866863093737e-13</v>
       </c>
       <c r="DM7" t="n">
-        <v>3.321207486806088e-07</v>
+        <v>3.569734636468987e-14</v>
       </c>
       <c r="DN7" t="n">
-        <v>4.301917215343565e-06</v>
+        <v>6.300198535612311e-14</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.339975708309794e-06</v>
+        <v>5.377693258691758e-14</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.319455918746826e-06</v>
+        <v>5.305655817033211e-14</v>
       </c>
       <c r="DQ7" t="n">
-        <v>2.132900362994405e-06</v>
+        <v>3.628035372127414e-13</v>
       </c>
       <c r="DR7" t="n">
-        <v>2.294428213645006e-06</v>
+        <v>1.614701888906847e-13</v>
       </c>
       <c r="DS7" t="n">
-        <v>3.456151944192243e-06</v>
+        <v>2.915743818263095e-13</v>
       </c>
       <c r="DT7" t="n">
-        <v>4.270482349966187e-06</v>
+        <v>1.722238074809007e-13</v>
       </c>
       <c r="DU7" t="n">
-        <v>2.643647576405783e-07</v>
+        <v>8.159586965513291e-14</v>
       </c>
       <c r="DV7" t="n">
-        <v>1.536428442250326e-07</v>
+        <v>6.564207863249752e-14</v>
       </c>
       <c r="DW7" t="n">
-        <v>2.258836673263431e-07</v>
+        <v>1.841656709945794e-13</v>
       </c>
       <c r="DX7" t="n">
-        <v>1.861775558609224e-06</v>
+        <v>1.850487468878052e-14</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.247449517904897e-06</v>
+        <v>2.227120668874677e-14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.428122115816223e-06</v>
+        <v>1.214457408336284e-13</v>
       </c>
       <c r="EA7" t="n">
-        <v>9.343003171125019e-07</v>
+        <v>8.985142545357011e-14</v>
       </c>
       <c r="EB7" t="n">
-        <v>3.124066097370815e-06</v>
+        <v>8.467709769043735e-14</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.895092106631637e-07</v>
+        <v>2.062431985177388e-13</v>
       </c>
       <c r="ED7" t="n">
-        <v>3.587301762308925e-06</v>
+        <v>4.828165048754302e-14</v>
       </c>
       <c r="EE7" t="n">
-        <v>2.299691686857841e-06</v>
+        <v>1.618756669506671e-13</v>
       </c>
       <c r="EF7" t="n">
-        <v>1.117180445930899e-07</v>
+        <v>2.467084425205462e-14</v>
       </c>
       <c r="EG7" t="n">
-        <v>3.863127631120733e-07</v>
+        <v>1.139509493708335e-13</v>
       </c>
       <c r="EH7" t="n">
-        <v>3.774566152969783e-07</v>
+        <v>1.340262942945911e-13</v>
       </c>
       <c r="EI7" t="n">
-        <v>3.326046680740546e-06</v>
+        <v>3.004816718794184e-13</v>
       </c>
       <c r="EJ7" t="n">
-        <v>1.301682800658455e-06</v>
+        <v>1.176751702807941e-13</v>
       </c>
       <c r="EK7" t="n">
-        <v>2.237807592564423e-07</v>
+        <v>3.628342201342227e-14</v>
       </c>
       <c r="EL7" t="n">
-        <v>1.981058403544012e-06</v>
+        <v>4.997774587299324e-14</v>
       </c>
       <c r="EM7" t="n">
-        <v>1.168674316431861e-06</v>
+        <v>7.558859679672458e-14</v>
       </c>
       <c r="EN7" t="n">
-        <v>2.979255668833503e-06</v>
+        <v>1.806284614068454e-13</v>
       </c>
       <c r="EO7" t="n">
-        <v>2.866115664801328e-06</v>
+        <v>1.439484788963094e-13</v>
       </c>
       <c r="EP7" t="n">
-        <v>5.485591373144416e-06</v>
+        <v>2.86471286145909e-13</v>
       </c>
       <c r="EQ7" t="n">
-        <v>2.67724954028381e-06</v>
+        <v>3.538696028912436e-13</v>
       </c>
       <c r="ER7" t="n">
-        <v>1.103528575185919e-06</v>
+        <v>8.638741984126966e-14</v>
       </c>
       <c r="ES7" t="n">
-        <v>4.010980319435475e-06</v>
+        <v>1.102743046074543e-13</v>
       </c>
       <c r="ET7" t="n">
-        <v>7.800173079886008e-06</v>
+        <v>2.700811037488482e-13</v>
       </c>
       <c r="EU7" t="n">
-        <v>1.555985363665968e-06</v>
+        <v>1.97849129115503e-13</v>
       </c>
       <c r="EV7" t="n">
-        <v>1.292966231858372e-07</v>
+        <v>1.443401875887013e-13</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.512955805083038e-06</v>
+        <v>1.279755517053296e-13</v>
       </c>
       <c r="EX7" t="n">
-        <v>6.741873335158743e-07</v>
+        <v>1.868289323161271e-13</v>
       </c>
       <c r="EY7" t="n">
-        <v>4.266904397809412e-06</v>
+        <v>4.579190217117446e-14</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.673992528594681e-06</v>
+        <v>1.134958555089327e-13</v>
       </c>
       <c r="FA7" t="n">
-        <v>1.789054522305378e-06</v>
+        <v>1.64597122823823e-13</v>
       </c>
       <c r="FB7" t="n">
-        <v>1.152692902905983e-06</v>
+        <v>3.329254190040376e-14</v>
       </c>
       <c r="FC7" t="n">
-        <v>8.238804412030731e-07</v>
+        <v>1.488016795284791e-13</v>
       </c>
       <c r="FD7" t="n">
-        <v>2.180803448936786e-07</v>
+        <v>1.030811991754171e-13</v>
       </c>
       <c r="FE7" t="n">
-        <v>6.371299718921364e-07</v>
+        <v>3.280500667662313e-14</v>
       </c>
       <c r="FF7" t="n">
-        <v>1.491089847149851e-06</v>
+        <v>1.554137948975992e-13</v>
       </c>
       <c r="FG7" t="n">
-        <v>2.772409857243474e-07</v>
+        <v>4.26756774449949e-13</v>
       </c>
       <c r="FH7" t="n">
-        <v>3.419227823542315e-06</v>
+        <v>1.574975366054263e-13</v>
       </c>
       <c r="FI7" t="n">
-        <v>2.573529400251573e-06</v>
+        <v>1.830979215900613e-13</v>
       </c>
       <c r="FJ7" t="n">
-        <v>2.600965217425255e-06</v>
+        <v>1.302377801958021e-13</v>
       </c>
       <c r="FK7" t="n">
-        <v>3.404112192129105e-07</v>
+        <v>8.386601282146453e-14</v>
       </c>
       <c r="FL7" t="n">
-        <v>2.681714249774814e-06</v>
+        <v>2.443039531525165e-13</v>
       </c>
       <c r="FM7" t="n">
-        <v>2.140999271205146e-07</v>
+        <v>2.441807606806679e-13</v>
       </c>
       <c r="FN7" t="n">
-        <v>3.932600066036684e-06</v>
+        <v>1.3828077138206e-14</v>
       </c>
       <c r="FO7" t="n">
-        <v>4.385956799524138e-06</v>
+        <v>2.105719705590772e-13</v>
       </c>
       <c r="FP7" t="n">
-        <v>1.789444581845601e-06</v>
+        <v>2.345415257409139e-14</v>
       </c>
       <c r="FQ7" t="n">
-        <v>1.204643467644928e-05</v>
+        <v>1.420394292635241e-13</v>
       </c>
       <c r="FR7" t="n">
-        <v>9.761301953403745e-07</v>
+        <v>1.862868176773572e-13</v>
       </c>
       <c r="FS7" t="n">
-        <v>1.366909145872341e-07</v>
+        <v>1.699435541293107e-13</v>
       </c>
       <c r="FT7" t="n">
-        <v>2.829451432262431e-06</v>
+        <v>2.544662885354404e-13</v>
       </c>
       <c r="FU7" t="n">
-        <v>9.150110713562754e-08</v>
+        <v>7.767449335636945e-14</v>
       </c>
       <c r="FV7" t="n">
-        <v>4.307084964239039e-07</v>
+        <v>3.028463981327723e-13</v>
       </c>
       <c r="FW7" t="n">
-        <v>2.989724180224584e-06</v>
+        <v>1.351799938263329e-13</v>
       </c>
       <c r="FX7" t="n">
-        <v>2.010544449149165e-06</v>
+        <v>1.38626469244757e-13</v>
       </c>
       <c r="FY7" t="n">
-        <v>1.375179749629751e-06</v>
+        <v>1.096821540384242e-13</v>
       </c>
       <c r="FZ7" t="n">
-        <v>6.268882316362578e-06</v>
+        <v>1.531643870978164e-13</v>
       </c>
       <c r="GA7" t="n">
-        <v>1.972564632524154e-06</v>
+        <v>7.581703819446728e-14</v>
       </c>
       <c r="GB7" t="n">
-        <v>6.373686119331978e-06</v>
+        <v>1.865704178606251e-13</v>
       </c>
       <c r="GC7" t="n">
-        <v>7.868298780522309e-06</v>
+        <v>9.848815285453533e-14</v>
       </c>
       <c r="GD7" t="n">
-        <v>6.92343292030273e-06</v>
+        <v>2.950070743246158e-13</v>
       </c>
       <c r="GE7" t="n">
-        <v>9.787692079044064e-07</v>
+        <v>3.874367325443565e-14</v>
       </c>
       <c r="GF7" t="n">
-        <v>3.438374506004038e-06</v>
+        <v>1.058697129529412e-13</v>
       </c>
       <c r="GG7" t="n">
-        <v>3.2296959489031e-06</v>
+        <v>1.517939284467404e-13</v>
       </c>
     </row>
     <row r="8">
@@ -4982,3416 +4982,3416 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.004785411059856415</v>
+        <v>0.0006152158603072166</v>
       </c>
       <c r="B9" t="n">
-        <v>0.06531395763158798</v>
+        <v>0.0009197094477713108</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009508531540632248</v>
+        <v>0.0001707807532511652</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03870194032788277</v>
+        <v>0.001537475851364434</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01565300673246384</v>
+        <v>0.0001739481958793476</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0168138537555933</v>
+        <v>0.001852647517807782</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007760744076222181</v>
+        <v>0.001111316494643688</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005461373366415501</v>
+        <v>0.0009249424911104143</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01049451436847448</v>
+        <v>3.458200808381662e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.01091488916426897</v>
+        <v>0.0005763620138168335</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05138257145881653</v>
+        <v>0.0006197276525199413</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002299725078046322</v>
+        <v>0.0002685864455997944</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03109109960496426</v>
+        <v>0.002455872017890215</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01505115907639265</v>
+        <v>0.0006068163784220815</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01850973814725876</v>
+        <v>0.002230152022093534</v>
       </c>
       <c r="P9" t="n">
-        <v>0.006229802034795284</v>
+        <v>0.001379432389512658</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.002768173813819885</v>
+        <v>0.0001907010737340897</v>
       </c>
       <c r="R9" t="n">
-        <v>0.01088484283536673</v>
+        <v>0.0002332011208636686</v>
       </c>
       <c r="S9" t="n">
-        <v>0.002440593903884292</v>
+        <v>0.000293958408292383</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005816345568746328</v>
+        <v>4.294220343581401e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002910527167841792</v>
+        <v>0.0004440771881490946</v>
       </c>
       <c r="V9" t="n">
-        <v>0.01156242191791534</v>
+        <v>3.000575816258788e-06</v>
       </c>
       <c r="W9" t="n">
-        <v>0.009832588955760002</v>
+        <v>0.0004124311089981347</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003937706351280212</v>
+        <v>0.0006237055058591068</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.006098262034356594</v>
+        <v>0.0001122409157687798</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.007636433001607656</v>
+        <v>0.0004293178499210626</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.009010631591081619</v>
+        <v>0.0002183357428293675</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0003319783136248589</v>
+        <v>0.0005658952286466956</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01138430833816528</v>
+        <v>0.0004130352172069252</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0030674715526402</v>
+        <v>0.0003982058551628143</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.002459316048771143</v>
+        <v>0.0001150394673459232</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0007842729683034122</v>
+        <v>0.000460888521047309</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.006075989454984665</v>
+        <v>0.0008130070054903626</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002424010075628757</v>
+        <v>0.0001611564366612583</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.001288533327169716</v>
+        <v>0.0006607325049117208</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.005080084782093763</v>
+        <v>0.0004427885578479618</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.00281362934038043</v>
+        <v>0.0002963216975331306</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.008593208156526089</v>
+        <v>0.0004889365518465638</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.00281317182816565</v>
+        <v>0.0006237841444090009</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.001182967913337052</v>
+        <v>0.000539327273145318</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.005762266460806131</v>
+        <v>4.60616429336369e-05</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.008243025280535221</v>
+        <v>0.0003888425708282739</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0006472578970715404</v>
+        <v>0.0003913622349500656</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0006610831478610635</v>
+        <v>0.0002170911029679701</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.008252731524407864</v>
+        <v>0.0002817194035742432</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.00409184955060482</v>
+        <v>0.0001750210794853047</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.03908899053931236</v>
+        <v>0.0004953208263032138</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.006647059228271246</v>
+        <v>0.0007012948044575751</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.01288715656846762</v>
+        <v>0.0009292695904150605</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.007926924154162407</v>
+        <v>0.001921958988532424</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01144749578088522</v>
+        <v>0.001492533832788467</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.006588460877537727</v>
+        <v>1.207364402944222e-05</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.00831021461635828</v>
+        <v>0.0002294603909831494</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.01100719347596169</v>
+        <v>7.488829578505829e-05</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.004212310072034597</v>
+        <v>0.0005204039043746889</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01169505435973406</v>
+        <v>0.0001422419736627489</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0121944472193718</v>
+        <v>4.982962855137885e-05</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.00475485110655427</v>
+        <v>0.0006052847020328045</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.01413264125585556</v>
+        <v>0.001199898310005665</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.005664796568453312</v>
+        <v>2.996441617142409e-05</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.009831210598349571</v>
+        <v>0.0003145622322335839</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.003669645171612501</v>
+        <v>0.0006682549137622118</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.008927760645747185</v>
+        <v>0.000183814627234824</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.002007106551900506</v>
+        <v>0.0002155641705030575</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.006129846908152103</v>
+        <v>0.0002793555322568864</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.006119255907833576</v>
+        <v>0.0001666346506681293</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0002418830990791321</v>
+        <v>0.0005233356496319175</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.003609659150242805</v>
+        <v>4.765280027640983e-05</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.00312410993501544</v>
+        <v>0.0001655501837376505</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.002434812020510435</v>
+        <v>2.751551801338792e-05</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.00386070110835135</v>
+        <v>0.0001402792404405773</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.003222111845389009</v>
+        <v>0.0003486376663204283</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.00386514188721776</v>
+        <v>1.782252365956083e-05</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.02042393013834953</v>
+        <v>0.0003550687397364527</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.009765134193003178</v>
+        <v>0.0003978441236540675</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.01193824969232082</v>
+        <v>0.001327680540271103</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.003963517490774393</v>
+        <v>0.0002619947481434792</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.001423708163201809</v>
+        <v>0.0008323790389113128</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0005630429368466139</v>
+        <v>0.000102060817880556</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.006369050592184067</v>
+        <v>9.610314009478316e-05</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.01167755853384733</v>
+        <v>0.000355519587174058</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.001131654484197497</v>
+        <v>5.844049519510008e-05</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0109143266454339</v>
+        <v>0.0002786816039588302</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.005658701527863741</v>
+        <v>0.0001558352523716167</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.005858710035681725</v>
+        <v>0.0006821213173680007</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0008341579232364893</v>
+        <v>6.462878809543326e-05</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.001525742118246853</v>
+        <v>0.0002652105467859656</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.001015382818877697</v>
+        <v>0.0001667467295192182</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.002094324212521315</v>
+        <v>0.0002771745785139501</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.004444791469722986</v>
+        <v>5.258165401755832e-05</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.008342793211340904</v>
+        <v>0.0001459674967918545</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0003058052971027792</v>
+        <v>8.889102900866419e-06</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0004449932603165507</v>
+        <v>0.000880023930221796</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.008371748030185699</v>
+        <v>0.001131271012127399</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.003972695674747229</v>
+        <v>0.0001261084398720413</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.004102357663214207</v>
+        <v>0.0001322563766734675</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.01083909533917904</v>
+        <v>8.44642345327884e-05</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.01036533061414957</v>
+        <v>0.0006683151586912572</v>
       </c>
       <c r="CU9" t="n">
-        <v>2.048419264610857e-05</v>
+        <v>0.0001433570869266987</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.001107280957512558</v>
+        <v>1.902354415506124e-05</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.01007055956870317</v>
+        <v>0.0002182612661272287</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.006403339561074972</v>
+        <v>2.336660691071302e-05</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.007302566431462765</v>
+        <v>0.0007381436880677938</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0002984018065035343</v>
+        <v>0.0001849436375778168</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.00264819897711277</v>
+        <v>0.0003142775385640562</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.001763657899573445</v>
+        <v>0.000193492291145958</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.003977438900619745</v>
+        <v>0.0002193118416471407</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.003152184886857867</v>
+        <v>0.0001242474099854007</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.003844395047053695</v>
+        <v>7.944954268168658e-05</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.009060834534466267</v>
+        <v>0.0002486389712430537</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001314011286012828</v>
+        <v>0.0004852207493968308</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.02452808432281017</v>
+        <v>0.0001481318613514304</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.01436865050345659</v>
+        <v>0.0002173671091441065</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.00730573944747448</v>
+        <v>0.0009109169477596879</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.008521710522472858</v>
+        <v>0.0001305151236010715</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.004199448972940445</v>
+        <v>0.001613280503079295</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.005995710380375385</v>
+        <v>0.0004344095941632986</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.001579012256115675</v>
+        <v>0.0001500116195529699</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.004320449661463499</v>
+        <v>0.0002559430431574583</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.001377336564473808</v>
+        <v>3.741342516150326e-05</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.002403292572125793</v>
+        <v>0.0001858263567555696</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.007365045137703419</v>
+        <v>0.0002423772966722026</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.002693088026717305</v>
+        <v>0.0001565120473969728</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.002919367980211973</v>
+        <v>0.0002865824208129197</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0006718180957250297</v>
+        <v>0.0006462937453761697</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.008753166534006596</v>
+        <v>0.0008191731758415699</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0008841520757414401</v>
+        <v>0.0001352420804323629</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001256497111171484</v>
+        <v>0.000129382184240967</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.007961338385939598</v>
+        <v>0.0005076510715298355</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.004622833803296089</v>
+        <v>0.0004494904424063861</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.002590762451291084</v>
+        <v>1.24603238873533e-05</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0002882182016037405</v>
+        <v>0.0006473195971921086</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.002945479936897755</v>
+        <v>0.0002763179363682866</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0005807370762340724</v>
+        <v>0.001003897283226252</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0006202322547324002</v>
+        <v>0.0009993999265134335</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001711568678729236</v>
+        <v>0.0004292158700991422</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.008147160522639751</v>
+        <v>8.927714952733368e-05</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.005580991972237825</v>
+        <v>0.0004925962421111763</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.004109143279492855</v>
+        <v>0.0006351465708576143</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.005050173960626125</v>
+        <v>4.141021781833842e-05</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.00302394013851881</v>
+        <v>8.989868365461007e-05</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.002046900568529963</v>
+        <v>6.107499939389527e-05</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.001129553071223199</v>
+        <v>6.863131420686841e-05</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.001019945018924773</v>
+        <v>1.033605803968385e-05</v>
       </c>
       <c r="EO9" t="n">
-        <v>0.001098847016692162</v>
+        <v>0.0002469195460435003</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.00854199193418026</v>
+        <v>0.0004716260300483555</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.006552938837558031</v>
+        <v>5.410562152974308e-06</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.003064647316932678</v>
+        <v>0.0005935393855907023</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.003216282231733203</v>
+        <v>1.928389247041196e-05</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.007120454683899879</v>
+        <v>0.0001351067912764847</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.008360874839127064</v>
+        <v>0.0003362865827511996</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.009868765249848366</v>
+        <v>0.0002716524759307504</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.002430569846183062</v>
+        <v>0.0009135575965046883</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0003421191941015422</v>
+        <v>5.837997741764411e-05</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.009661117568612099</v>
+        <v>0.0002686225052457303</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.004159933887422085</v>
+        <v>0.0001007160608423874</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.007392507046461105</v>
+        <v>0.0008133084047585726</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0009191593271680176</v>
+        <v>3.545781146385707e-05</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.002255040220916271</v>
+        <v>0.0002588053757790476</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.003149561351165175</v>
+        <v>0.0002847995201591402</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.003234139643609524</v>
+        <v>0.0003114930004812777</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.005933515727519989</v>
+        <v>6.725900311721489e-05</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0003075207932852209</v>
+        <v>4.849961260333657e-05</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.002300230087712407</v>
+        <v>0.0001876944734249264</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.004908919800072908</v>
+        <v>0.00028321921126917</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.004147398751229048</v>
+        <v>0.0002842113026417792</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.003080868627876043</v>
+        <v>0.0001526925625512376</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.002797541441395879</v>
+        <v>1.979015360120684e-05</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0003648523706942797</v>
+        <v>0.0001567895378684625</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.003631620667874813</v>
+        <v>0.0003069395897909999</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0002930221962742507</v>
+        <v>0.0005903927376493812</v>
       </c>
       <c r="FP9" t="n">
-        <v>0.005226888228207827</v>
+        <v>0.0006398377590812743</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.007256315089762211</v>
+        <v>0.0009482476743869483</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.00800718180835247</v>
+        <v>0.001043734373524785</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0006304251728579402</v>
+        <v>0.0009346099104732275</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.008300689980387688</v>
+        <v>0.000888024689629674</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.001705910661257803</v>
+        <v>0.0006284185219556093</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.004659323953092098</v>
+        <v>7.188267773017287e-06</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.005869955290108919</v>
+        <v>0.001974354032427073</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0009522770415060222</v>
+        <v>2.357282937737182e-05</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.009309620596468449</v>
+        <v>0.0001587540755281225</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0007681925781071186</v>
+        <v>0.0004713471280410886</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.004682851023972034</v>
+        <v>0.0002468315069563687</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0004195044748485088</v>
+        <v>0.000746445613913238</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.009698274545371532</v>
+        <v>0.0002309282426722348</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.007829770445823669</v>
+        <v>0.0006832910003140569</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.02422360330820084</v>
+        <v>0.0005162404850125313</v>
       </c>
       <c r="GF9" t="n">
-        <v>0.003241591388359666</v>
+        <v>0.0002628391375765204</v>
       </c>
       <c r="GG9" t="n">
-        <v>8.725019870325923e-05</v>
+        <v>0.0002873117045965046</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.4579848647117615</v>
+        <v>0.008214009925723076</v>
       </c>
       <c r="B10" t="n">
-        <v>3.421915531158447</v>
+        <v>0.027530487626791</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2427121847867966</v>
+        <v>8.688624075148255e-05</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8443936109542847</v>
+        <v>0.08250535279512405</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5299092531204224</v>
+        <v>0.02472260408103466</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4749875068664551</v>
+        <v>0.01343483570963144</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2306134104728699</v>
+        <v>0.04639249667525291</v>
       </c>
       <c r="H10" t="n">
-        <v>0.350551962852478</v>
+        <v>0.03600373864173889</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07819501310586929</v>
+        <v>0.02485315315425396</v>
       </c>
       <c r="J10" t="n">
-        <v>0.624555766582489</v>
+        <v>0.01152173522859812</v>
       </c>
       <c r="K10" t="n">
-        <v>1.97644567489624</v>
+        <v>0.008132998831570148</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0688648447394371</v>
+        <v>0.0002949123736470938</v>
       </c>
       <c r="M10" t="n">
-        <v>1.365852117538452</v>
+        <v>0.1156956627964973</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2595424652099609</v>
+        <v>0.04701367020606995</v>
       </c>
       <c r="O10" t="n">
-        <v>1.07955002784729</v>
+        <v>0.01142531540244818</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2461727410554886</v>
+        <v>0.0490034818649292</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1484040915966034</v>
+        <v>0.02123365364968777</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1727301478385925</v>
+        <v>0.03039438650012016</v>
       </c>
       <c r="S10" t="n">
-        <v>0.04660110548138618</v>
+        <v>0.005471959710121155</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4304267764091492</v>
+        <v>0.00200387928634882</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1093169450759888</v>
+        <v>0.005187600385397673</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3115159273147583</v>
+        <v>0.01115146838128567</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1672337055206299</v>
+        <v>0.02109136059880257</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3267711699008942</v>
+        <v>0.002138013485819101</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.05963800847530365</v>
+        <v>0.004038461018353701</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5539475083351135</v>
+        <v>0.003733131568878889</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.3428489863872528</v>
+        <v>0.002908271504566073</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.1657705903053284</v>
+        <v>0.003039302304387093</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.4342342913150787</v>
+        <v>0.002117001684382558</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.490580677986145</v>
+        <v>0.006359920836985111</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.003915391862392426</v>
+        <v>0.005362472031265497</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.4428072273731232</v>
+        <v>0.003848819062113762</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.2193180471658707</v>
+        <v>0.001635658089071512</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.2222060710191727</v>
+        <v>0.01116952486336231</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.2416942715644836</v>
+        <v>0.009282019920647144</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0381002277135849</v>
+        <v>0.007567856926470995</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.4752272665500641</v>
+        <v>0.006711402907967567</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.1844466179609299</v>
+        <v>0.01643151417374611</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.2531097531318665</v>
+        <v>0.007265030406415462</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.4052146673202515</v>
+        <v>0.01637955568730831</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.2434308230876923</v>
+        <v>0.006003530696034431</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.2032228261232376</v>
+        <v>0.005393978208303452</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.08654859662055969</v>
+        <v>0.02282164618372917</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.2428421378135681</v>
+        <v>0.005650379229336977</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.09929902851581573</v>
+        <v>0.001821086159907281</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.02828305214643478</v>
+        <v>0.02628369629383087</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.65886926651001</v>
+        <v>0.01817002147436142</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1287001818418503</v>
+        <v>0.008217014372348785</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.1918876320123672</v>
+        <v>0.02190166339278221</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.9122968316078186</v>
+        <v>0.05627141520380974</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.1226783245801926</v>
+        <v>0.006637940648943186</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1439353972673416</v>
+        <v>0.002994388341903687</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.4164531230926514</v>
+        <v>0.0007583808619529009</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.08821909129619598</v>
+        <v>0.01611020416021347</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.1635971367359161</v>
+        <v>0.000769865233451128</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.6286189556121826</v>
+        <v>1.949630677700043e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.4834226667881012</v>
+        <v>0.005027804058045149</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.2988125383853912</v>
+        <v>0.01344022247940302</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.8022705316543579</v>
+        <v>0.00247653666883707</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.2933965623378754</v>
+        <v>5.17219741595909e-05</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.06238115951418877</v>
+        <v>0.01477612368762493</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.3342824578285217</v>
+        <v>0.01235202420502901</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.1370627731084824</v>
+        <v>0.007915210910141468</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.7657926082611084</v>
+        <v>0.003541921498253942</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.775960385799408</v>
+        <v>0.002631629584357142</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.4251776337623596</v>
+        <v>0.008290019817650318</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.4603954553604126</v>
+        <v>0.02128205075860023</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.506557285785675</v>
+        <v>0.008868432603776455</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.1215766668319702</v>
+        <v>0.01022871769964695</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.000681757926940918</v>
+        <v>0.001457802951335907</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.1746088564395905</v>
+        <v>0.003470233641564846</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.2705256938934326</v>
+        <v>0.00272507406771183</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.1517038345336914</v>
+        <v>0.008302172645926476</v>
       </c>
       <c r="BV10" t="n">
-        <v>1.172972321510315</v>
+        <v>0.01808370836079121</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.002627946436405182</v>
+        <v>0.007180220913141966</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.2413825243711472</v>
+        <v>0.04235943779349327</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.4637473225593567</v>
+        <v>0.02190205827355385</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.5192639827728271</v>
+        <v>0.002403899095952511</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.2385213971138</v>
+        <v>0.003809082787483931</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.03609398752450943</v>
+        <v>9.94107685983181e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.3155180215835571</v>
+        <v>0.006445075385272503</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.261329859495163</v>
+        <v>0.002491619903594255</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.5812427997589111</v>
+        <v>0.00179396360181272</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.1303350329399109</v>
+        <v>0.004075200296938419</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.02710603736341</v>
+        <v>0.0266314297914505</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.2941150367259979</v>
+        <v>0.005148893222212791</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02329411916434765</v>
+        <v>0.0007666372694075108</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.04900646209716797</v>
+        <v>0.002131641609594226</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.005365632474422455</v>
+        <v>0.007992884144186974</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.02292392030358315</v>
+        <v>0.002192398300394416</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.5402891635894775</v>
+        <v>0.01376273296773434</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.5379021763801575</v>
+        <v>0.004796659108251333</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.2344922423362732</v>
+        <v>0.00612071854993701</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.7848216891288757</v>
+        <v>0.03241678327322006</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.4209664463996887</v>
+        <v>0.03202123939990997</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.7108049392700195</v>
+        <v>0.005607252474874258</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.1841716766357422</v>
+        <v>0.02358105033636093</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.1288821697235107</v>
+        <v>0.004245096817612648</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.1123542562127113</v>
+        <v>0.01184107176959515</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.263139933347702</v>
+        <v>0.003117151791229844</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.4679365456104279</v>
+        <v>0.001483758329413831</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.1153613477945328</v>
+        <v>0.002831528661772609</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.1276547312736511</v>
+        <v>0.02836478315293789</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.4035972356796265</v>
+        <v>0.008968928828835487</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.05707046762108803</v>
+        <v>0.0008900635875761509</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0746186152100563</v>
+        <v>6.885442417114973e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.04086959362030029</v>
+        <v>0.006700364407151937</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.04609106481075287</v>
+        <v>0.0047855069860816</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1560661494731903</v>
+        <v>0.02489395998418331</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.2966148257255554</v>
+        <v>0.0005260782199911773</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.2900713682174683</v>
+        <v>0.009988259524106979</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.001359634101390839</v>
+        <v>0.04220779612660408</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1027947068214417</v>
+        <v>0.008748902939260006</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.2020589113235474</v>
+        <v>0.02559736929833889</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.1234484538435936</v>
+        <v>0.005939360242336988</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.02953052148222923</v>
+        <v>0.02404955588281155</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.03698958083987236</v>
+        <v>2.751406282186508e-05</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.3327633440494537</v>
+        <v>0.01004278659820557</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.04606333374977112</v>
+        <v>0.004531744867563248</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.4292694628238678</v>
+        <v>0.008057252503931522</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.07787062972784042</v>
+        <v>0.009926570579409599</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.209170326590538</v>
+        <v>0.001269807806238532</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.5489481687545776</v>
+        <v>0.005200430750846863</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.051629938185215</v>
+        <v>0.006378527730703354</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.3286130726337433</v>
+        <v>0.01206918153911829</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.06110271066427231</v>
+        <v>0.02559724263846874</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2247636914253235</v>
+        <v>0.005232208408415318</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.1647467613220215</v>
+        <v>0.00528528168797493</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.4611459374427795</v>
+        <v>0.01664545945823193</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.05334829911589622</v>
+        <v>0.01377260126173496</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.5623834133148193</v>
+        <v>0.002588503295555711</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.3370214104652405</v>
+        <v>0.006538976915180683</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.101107120513916</v>
+        <v>0.003253640606999397</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.08391360193490982</v>
+        <v>0.01885851286351681</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.1054017469286919</v>
+        <v>0.001526607782579958</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.3187261819839478</v>
+        <v>0.01430666074156761</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.6981506943702698</v>
+        <v>0.0007972167804837227</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.1864461600780487</v>
+        <v>0.003189516952261329</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.06618285179138184</v>
+        <v>0.0224476046860218</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.192965105175972</v>
+        <v>0.004836784210056067</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.1277605295181274</v>
+        <v>0.001835057977586985</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.06457316130399704</v>
+        <v>0.006523358169943094</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.02529794722795486</v>
+        <v>0.006307146511971951</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.1537914723157883</v>
+        <v>0.006550805643200874</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.1400665044784546</v>
+        <v>0.007323472294956446</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.2851600646972656</v>
+        <v>0.007596179377287626</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.1543286144733429</v>
+        <v>0.002749877516180277</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.1911634802818298</v>
+        <v>0.03103745356202126</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.5431419014930725</v>
+        <v>0.005801609251648188</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.6593925356864929</v>
+        <v>0.01001683808863163</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.2463985532522202</v>
+        <v>0.003988131415098906</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.3647816777229309</v>
+        <v>0.004040716215968132</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.1693204194307327</v>
+        <v>0.01904909871518612</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.208062469959259</v>
+        <v>0.003128028940409422</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.5207213759422302</v>
+        <v>0.003429125994443893</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.04756773263216019</v>
+        <v>0.001627317979000509</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01256264746189117</v>
+        <v>0.03136249631643295</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.1920877397060394</v>
+        <v>0.00839214026927948</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.1043529435992241</v>
+        <v>0.002553871367126703</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.08898127824068069</v>
+        <v>0.0009219959611073136</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.01611050218343735</v>
+        <v>0.008944759145379066</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.02861223183572292</v>
+        <v>0.002827130723744631</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.228925809264183</v>
+        <v>0.006430576555430889</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.2444266676902771</v>
+        <v>0.001329385209828615</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.06130684167146683</v>
+        <v>0.001356551656499505</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.1533127576112747</v>
+        <v>0.003281038720160723</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.2953854501247406</v>
+        <v>0.001819130964577198</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.1379604041576385</v>
+        <v>0.0005799417849630117</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.1346945464611053</v>
+        <v>0.006108461413532495</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.1360448747873306</v>
+        <v>0.007889168336987495</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.1644273847341537</v>
+        <v>0.01575897634029388</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.1441007256507874</v>
+        <v>0.01157926395535469</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.5751029849052429</v>
+        <v>0.02476412430405617</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.04259245842695236</v>
+        <v>0.003852448426187038</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.4663733541965485</v>
+        <v>0.009637476876378059</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.1202788054943085</v>
+        <v>0.01101355440914631</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.3889542818069458</v>
+        <v>0.009387379512190819</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.2776714563369751</v>
+        <v>0.01604732498526573</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.5029103755950928</v>
+        <v>0.03009027801454067</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.04367944225668907</v>
+        <v>0.009969327598810196</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.4319815039634705</v>
+        <v>0.004215527325868607</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.1324585974216461</v>
+        <v>0.005683871451765299</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.08970380574464798</v>
+        <v>0.009800393134355545</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.1565422266721725</v>
+        <v>0.01789769344031811</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.03353118523955345</v>
+        <v>0.007962100207805634</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.3432328701019287</v>
+        <v>0.01228580996394157</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.640378475189209</v>
+        <v>0.007336095906794071</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.3483477234840393</v>
+        <v>0.005435552448034286</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.003223132342100143</v>
+        <v>0.01131126470863819</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.002523351460695267</v>
+        <v>0.02823587507009506</v>
       </c>
       <c r="B11" t="n">
-        <v>0.07281702011823654</v>
+        <v>0.05762495473027229</v>
       </c>
       <c r="C11" t="n">
-        <v>0.006040370091795921</v>
+        <v>0.008049281314015388</v>
       </c>
       <c r="D11" t="n">
-        <v>0.03190439194440842</v>
+        <v>0.02404965832829475</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01819773577153683</v>
+        <v>0.002795029431581497</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05671674758195877</v>
+        <v>0.06728122383356094</v>
       </c>
       <c r="G11" t="n">
-        <v>0.006170190405100584</v>
+        <v>0.0146284531801939</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02903575822710991</v>
+        <v>0.03017308004200459</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001396904466673732</v>
+        <v>0.003322620177641511</v>
       </c>
       <c r="J11" t="n">
-        <v>0.009581746533513069</v>
+        <v>0.02376456931233406</v>
       </c>
       <c r="K11" t="n">
-        <v>0.06409283727407455</v>
+        <v>0.06679447740316391</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001630811486393213</v>
+        <v>0.01573772914707661</v>
       </c>
       <c r="M11" t="n">
-        <v>0.02588959783315659</v>
+        <v>0.005171994678676128</v>
       </c>
       <c r="N11" t="n">
-        <v>0.002667339984327555</v>
+        <v>0.02905118279159069</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05497059971094131</v>
+        <v>0.07385086268186569</v>
       </c>
       <c r="P11" t="n">
-        <v>0.005525434389710426</v>
+        <v>0.009008215740323067</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01090516988188028</v>
+        <v>0.01116346661001444</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0004186881997156888</v>
+        <v>0.01900604367256165</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002029633615165949</v>
+        <v>0.003928212448954582</v>
       </c>
       <c r="T11" t="n">
-        <v>0.005195054225623608</v>
+        <v>0.0116479080170393</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0002979196142405272</v>
+        <v>0.0116266505792737</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01229070499539375</v>
+        <v>0.0145951434969902</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01591245085000992</v>
+        <v>0.01222812570631504</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001616558991372585</v>
+        <v>0.006698855198919773</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.003504664404317737</v>
+        <v>0.001798630459234118</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.006241098046302795</v>
+        <v>0.008839556947350502</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.00633116252720356</v>
+        <v>0.005566883366554976</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.252636037766933e-05</v>
+        <v>0.00156777014490217</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.00412042299285531</v>
+        <v>0.009474977850914001</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.001863370416685939</v>
+        <v>0.002905114786699414</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.003970462828874588</v>
+        <v>0.01397803984582424</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.006424773018807173</v>
+        <v>0.02908977493643761</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.006522891111671925</v>
+        <v>0.01135275978595018</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0009267558343708515</v>
+        <v>0.01189623773097992</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.003019107505679131</v>
+        <v>0.03132514655590057</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.004170420113950968</v>
+        <v>0.005090094637125731</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.009469533339142799</v>
+        <v>0.0005112094804644585</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.009140579961240292</v>
+        <v>0.01797343976795673</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.003592010121792555</v>
+        <v>0.01600817032158375</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0007847498636692762</v>
+        <v>0.009172571823000908</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0006042813183739781</v>
+        <v>0.001665401272475719</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.01308280695229769</v>
+        <v>0.006764544639736414</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.002173536224290729</v>
+        <v>0.003281690878793597</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.005116630345582962</v>
+        <v>0.007780278101563454</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.006320243701338768</v>
+        <v>0.004668304696679115</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.003477287944406271</v>
+        <v>0.01285296771675348</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.05029768869280815</v>
+        <v>0.06191419064998627</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.002204193733632565</v>
+        <v>0.01763426698744297</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.01067306939512491</v>
+        <v>0.0003943588235415518</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0103005189448595</v>
+        <v>0.02615977264940739</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.02980122715234756</v>
+        <v>0.03858515247702599</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0144027266651392</v>
+        <v>0.0002596266567707062</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0002016283106058836</v>
+        <v>0.01111540663987398</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.004175396636128426</v>
+        <v>0.005029604770243168</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0003112056292593479</v>
+        <v>0.0002699366305023432</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.02404507249593735</v>
+        <v>0.005062508396804333</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.01642853766679764</v>
+        <v>0.01186133734881878</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.880133878439665e-05</v>
+        <v>0.01748408749699593</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.01156158186495304</v>
+        <v>0.00223488244228065</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.01836494542658329</v>
+        <v>0.00806026253849268</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.008281122893095016</v>
+        <v>0.0009107801597565413</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.003162482520565391</v>
+        <v>0.01887262426316738</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.004748777486383915</v>
+        <v>0.005956719163805246</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.007710183504968882</v>
+        <v>0.0008723686914891005</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.01991172134876251</v>
+        <v>0.01530340034514666</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.004444137215614319</v>
+        <v>0.002364848740398884</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.0001109540462493896</v>
+        <v>0.001577381393872201</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.006203819997608662</v>
+        <v>0.0132551547139883</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.002788731828331947</v>
+        <v>0.01331380847841501</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.004304485395550728</v>
+        <v>0.01986169815063477</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.009714061394333839</v>
+        <v>0.005955475848168135</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.002812004648149014</v>
+        <v>0.01841037534177303</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.00440661795437336</v>
+        <v>0.0005008014850318432</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.02793118357658386</v>
+        <v>0.04296106845140457</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.003739431034773588</v>
+        <v>0.009456336498260498</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.01002043671905994</v>
+        <v>0.01807845756411552</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.001208984293043613</v>
+        <v>0.007325243670493364</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.009285642765462399</v>
+        <v>0.02374828048050404</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.003081472590565681</v>
+        <v>0.005216479301452637</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.003773362841457129</v>
+        <v>0.002988772001117468</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.004597455263137817</v>
+        <v>0.008142386563122272</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0007696010870859027</v>
+        <v>0.01171026099473238</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.01081119664013386</v>
+        <v>0.01947705633938313</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.004629408475011587</v>
+        <v>0.001483635394833982</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.004821871407330036</v>
+        <v>0.004425547085702419</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0006930115632712841</v>
+        <v>0.003178454004228115</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.009394615888595581</v>
+        <v>0.01664833724498749</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.005653659347444773</v>
+        <v>0.006630029529333115</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.00699986657127738</v>
+        <v>0.004274097271263599</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.004823201801627874</v>
+        <v>0.004105761647224426</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.01305003836750984</v>
+        <v>0.0008592009544372559</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.01242872700095177</v>
+        <v>0.02819316834211349</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0002165373880416155</v>
+        <v>0.02117348462343216</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.00943378359079361</v>
+        <v>0.02077550813555717</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.001985516166314483</v>
+        <v>0.01135012414306402</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.004754066001623869</v>
+        <v>0.00465918704867363</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.01165633648633957</v>
+        <v>0.01256935950368643</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.01327299419790506</v>
+        <v>0.008272581733763218</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.002588554751127958</v>
+        <v>0.0007742751622572541</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0004808695521205664</v>
+        <v>0.007953734137117863</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.008412711322307587</v>
+        <v>0.01587890461087227</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.004426936618983746</v>
+        <v>0.0002170207444578409</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.007872167974710464</v>
+        <v>0.002541154623031616</v>
       </c>
       <c r="CZ11" t="n">
-        <v>5.409732693806291e-05</v>
+        <v>0.0003742831759154797</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.009027101099491119</v>
+        <v>0.0175489317625761</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.004821630194783211</v>
+        <v>0.003362284507602453</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.009975369088351727</v>
+        <v>0.004861020483076572</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.001958680804818869</v>
+        <v>0.002319997875019908</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.004519997164607048</v>
+        <v>0.002336056437343359</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.009379184804856777</v>
+        <v>0.01685532182455063</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.002946229884400964</v>
+        <v>0.007774569094181061</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.02941153198480606</v>
+        <v>0.000390172004699707</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02200022898614407</v>
+        <v>0.01321292389184237</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.006101273465901613</v>
+        <v>0.002237590495496988</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.01326491497457027</v>
+        <v>0.004109031520783901</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.01183638349175453</v>
+        <v>0.02357338555157185</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.01891184411942959</v>
+        <v>0.02480963245034218</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.001927845063619316</v>
+        <v>0.001088384073227644</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.004097322933375835</v>
+        <v>0.009349212050437927</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.005700455512851477</v>
+        <v>0.008560223504900932</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.0002690311521291733</v>
+        <v>0.008363239467144012</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.001483368105255067</v>
+        <v>0.005033442284911871</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.002436913084238768</v>
+        <v>0.01004857663065195</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0003558473836164922</v>
+        <v>0.0008533968939445913</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.001082577859051526</v>
+        <v>0.01856039464473724</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.001800675294362009</v>
+        <v>0.008779737167060375</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0002224954077973962</v>
+        <v>0.004457630217075348</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0001712956000119448</v>
+        <v>0.001586209749802947</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.001929591177031398</v>
+        <v>0.009251232258975506</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.003344300203025341</v>
+        <v>0.00721374386921525</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.001711837016046047</v>
+        <v>0.0003514145500957966</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.006993784569203854</v>
+        <v>0.01568452827632427</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.001105634961277246</v>
+        <v>3.109010867774487e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0006164039950817823</v>
+        <v>0.003742924425750971</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.005975584499537945</v>
+        <v>0.02368630655109882</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.001365508418530226</v>
+        <v>0.008698794990777969</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.008456510491669178</v>
+        <v>0.0008533411892130971</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.002885882277041674</v>
+        <v>0.009588112123310566</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.003049247665330768</v>
+        <v>0.008128643967211246</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.005031582899391651</v>
+        <v>0.008555221371352673</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.008059365674853325</v>
+        <v>0.009106883779168129</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.004298615735024214</v>
+        <v>0.002261020243167877</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.002636656630784273</v>
+        <v>0.002541432389989495</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.002385216765105724</v>
+        <v>0.002887984504923224</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.003194279037415981</v>
+        <v>0.01238960213959217</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.003572911024093628</v>
+        <v>0.01383094489574432</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.003484253771603107</v>
+        <v>0.003051427425816655</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.007477376144379377</v>
+        <v>0.007554138079285622</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.004769839346408844</v>
+        <v>0.0186781994998455</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.009212703444063663</v>
+        <v>0.01064762007445097</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.00849333219230175</v>
+        <v>0.002609093207865953</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.02072001993656158</v>
+        <v>0.006948864087462425</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.001305469777435064</v>
+        <v>0.00296273548156023</v>
       </c>
       <c r="EX11" t="n">
-        <v>4.340277519077063e-05</v>
+        <v>0.01232047192752361</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.007560973986983299</v>
+        <v>0.02096522226929665</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.002573669655248523</v>
+        <v>3.616273170337081e-05</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.006185645237565041</v>
+        <v>0.001485278364270926</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0009189149714075029</v>
+        <v>0.002738559152930975</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.009255463257431984</v>
+        <v>0.01495023630559444</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.007737664040178061</v>
+        <v>0.006949407979846001</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.008050135336816311</v>
+        <v>0.00422236230224371</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.004199169110506773</v>
+        <v>0.004146449267864227</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0009680470102466643</v>
+        <v>0.004076605662703514</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.004354287404567003</v>
+        <v>0.02015404030680656</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.001092619728296995</v>
+        <v>0.009789947420358658</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.01130884140729904</v>
+        <v>0.01190128922462463</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0004029474221169949</v>
+        <v>0.01175387110561132</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.002323185093700886</v>
+        <v>0.02436713315546513</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.003784888191148639</v>
+        <v>0.01095367502421141</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.001887709833681583</v>
+        <v>0.04077756404876709</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.001907600671984255</v>
+        <v>0.01638756133615971</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.007997907698154449</v>
+        <v>0.002850182820111513</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.005106039345264435</v>
+        <v>0.02295289374887943</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.006186880171298981</v>
+        <v>0.02158451080322266</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.004508732352405787</v>
+        <v>0.01966059394180775</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.01113145612180233</v>
+        <v>0.004726415034383535</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01121143624186516</v>
+        <v>0.0134668555110693</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.01047254353761673</v>
+        <v>0.00618872232735157</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.001520180143415928</v>
+        <v>0.0385315790772438</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.002951953327283263</v>
+        <v>0.0116501422598958</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.009687216952443123</v>
+        <v>0.01393656060099602</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.001893731532618403</v>
+        <v>0.00365256704390049</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.002675845753401518</v>
+        <v>0.01366517413407564</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0008528433972969651</v>
+        <v>0.002968644257634878</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.007645869627594948</v>
+        <v>0.01691103540360928</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.01001482736319304</v>
+        <v>0.017707334831357</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.01951874978840351</v>
+        <v>0.0002675214491318911</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0002345271641388535</v>
+        <v>0.00497127091512084</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.0003333883068989962</v>
+        <v>0.01423902437090874</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.005460030399262905</v>
+        <v>7.349309453275055e-05</v>
       </c>
       <c r="B12" t="n">
-        <v>0.05280204862356186</v>
+        <v>0.001658126246184111</v>
       </c>
       <c r="C12" t="n">
-        <v>0.004853290971368551</v>
+        <v>0.0002971680951304734</v>
       </c>
       <c r="D12" t="n">
-        <v>0.03464989736676216</v>
+        <v>0.002221785951405764</v>
       </c>
       <c r="E12" t="n">
-        <v>0.005980200134217739</v>
+        <v>0.0003203971427865326</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007623841520398855</v>
+        <v>0.001332194311544299</v>
       </c>
       <c r="G12" t="n">
-        <v>0.00846805889159441</v>
+        <v>0.001433559926226735</v>
       </c>
       <c r="H12" t="n">
-        <v>0.005205613560974598</v>
+        <v>0.001295378664508462</v>
       </c>
       <c r="I12" t="n">
-        <v>0.004037462174892426</v>
+        <v>0.0004575378261506557</v>
       </c>
       <c r="J12" t="n">
-        <v>0.009791787713766098</v>
+        <v>0.0001236433017766103</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03795716539025307</v>
+        <v>0.001088408404029906</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0002239152527181432</v>
+        <v>0.0005038212984800339</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02947114780545235</v>
+        <v>0.003164088353514671</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01296728570014238</v>
+        <v>0.001269441796466708</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01413424219936132</v>
+        <v>0.001347969868220389</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0026837307959795</v>
+        <v>0.001652298029512167</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.005204543005675077</v>
+        <v>0.0008540925337001681</v>
       </c>
       <c r="R12" t="n">
-        <v>0.005009068641811609</v>
+        <v>0.0002698545577004552</v>
       </c>
       <c r="S12" t="n">
-        <v>0.002389909932389855</v>
+        <v>9.206730464939028e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>0.007640112657099962</v>
+        <v>1.516762131359428e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.002020495478063822</v>
+        <v>0.0003683512913994491</v>
       </c>
       <c r="V12" t="n">
-        <v>0.005986384116113186</v>
+        <v>0.0002559463609941304</v>
       </c>
       <c r="W12" t="n">
-        <v>0.003250276204198599</v>
+        <v>0.0004118377109989524</v>
       </c>
       <c r="X12" t="n">
-        <v>0.004093717783689499</v>
+        <v>0.0004550248559098691</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.006699937861412764</v>
+        <v>0.0001102946334867738</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.002695237984880805</v>
+        <v>0.000294949539238587</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.005715261679142714</v>
+        <v>7.229440234368667e-05</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.002322747837752104</v>
+        <v>0.0001716010447125882</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01012785453349352</v>
+        <v>0.0001548104046378285</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.001813132083043456</v>
+        <v>0.0003216254408471286</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.001142690423876047</v>
+        <v>0.000223467024625279</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.001402397407218814</v>
+        <v>0.0005598232382908463</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0005761455395258963</v>
+        <v>0.0008533842628821731</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.006737926974892616</v>
+        <v>0.0004268171032890677</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0005350022693164647</v>
+        <v>0.0004980392404831946</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.002444154117256403</v>
+        <v>0.0003099638561252505</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.005081765353679657</v>
+        <v>0.0001333485706709325</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.00699616177007556</v>
+        <v>0.0006719406228512526</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0001600726536707953</v>
+        <v>0.000514960614964366</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.003209324320778251</v>
+        <v>0.0004338245489634573</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.004395507276058197</v>
+        <v>1.182020059786737e-05</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.004962841514497995</v>
+        <v>0.0004655039228964597</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.001924590324051678</v>
+        <v>0.0004294338286854327</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.001507728127762675</v>
+        <v>0.0001970779558178037</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.002241628710180521</v>
+        <v>0.0001155674617621116</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.00367656210437417</v>
+        <v>0.0005592029774561524</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.03806880861520767</v>
+        <v>0.0007794894627295434</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.001521203201264143</v>
+        <v>0.0008640623418614268</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.007513222750276327</v>
+        <v>0.0006118674064055085</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.005072045139968395</v>
+        <v>0.002026289934292436</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.003820053767412901</v>
+        <v>0.00121205230243504</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.002320947125554085</v>
+        <v>0.0001999417290790007</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0006009371136315167</v>
+        <v>6.671763549093157e-05</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.003119384171441197</v>
+        <v>0.0002369141875533387</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.0004082424566149712</v>
+        <v>5.777654587291181e-05</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.007625196129083633</v>
+        <v>0.0003216884506400675</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.007737045176327229</v>
+        <v>8.187800995074213e-05</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.005538720171898603</v>
+        <v>0.0002754692395683378</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.01733459532260895</v>
+        <v>0.0008937845705077052</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.990122634917498e-06</v>
+        <v>9.916287672240287e-05</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.01035288628190756</v>
+        <v>0.0004750786465592682</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.004958489909768105</v>
+        <v>0.0005851890309713781</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.005471874494105577</v>
+        <v>0.0002618468715809286</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.005838175304234028</v>
+        <v>0.0001546080020489171</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.005083749070763588</v>
+        <v>0.0003125412040390074</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.003862782614305615</v>
+        <v>0.000144474150147289</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.003927381709218025</v>
+        <v>0.0004785201454069465</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.004772151820361614</v>
+        <v>0.0001713540405035019</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.002538402564823627</v>
+        <v>6.925743946339935e-05</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.005370783619582653</v>
+        <v>0.0001241071149706841</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.004277621861547232</v>
+        <v>2.489793951099273e-05</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.002095180563628674</v>
+        <v>0.0001423434150638059</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.003921977244317532</v>
+        <v>0.0001395197177771479</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.01829387992620468</v>
+        <v>0.0006565793883055449</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.003990655299276114</v>
+        <v>0.0004697685944847763</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.006311842706054449</v>
+        <v>0.0009781827684491873</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.001341844792477787</v>
+        <v>0.0004096628108527511</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.002714172936975956</v>
+        <v>0.0008192163659259677</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.001744135865010321</v>
+        <v>0.0003511450195219368</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.001910978928208351</v>
+        <v>6.780740659451112e-05</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.004657157231122255</v>
+        <v>6.003629096085206e-05</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.00230748625472188</v>
+        <v>3.752251359401271e-05</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.009173620492219925</v>
+        <v>0.0003698500222526491</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.003837909549474716</v>
+        <v>7.934475434012711e-05</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.003198492573574185</v>
+        <v>0.0007954289321787655</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.00301161059178412</v>
+        <v>4.689690103987232e-05</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.001868810155428946</v>
+        <v>0.0002634242991916835</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.003287613391876221</v>
+        <v>5.90688159718411e-06</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.001920934533700347</v>
+        <v>0.0003065532655455172</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.002517853165045381</v>
+        <v>0.0001525446714367718</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.01136799529194832</v>
+        <v>0.0003235838958062232</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.003175202291458845</v>
+        <v>1.998404695768841e-05</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.003179429098963737</v>
+        <v>0.00081923499237746</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.01001961436122656</v>
+        <v>0.00107610085979104</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.007674350403249264</v>
+        <v>0.0001875639136414975</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.005348740145564079</v>
+        <v>0.0003688080469146371</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.005328534170985222</v>
+        <v>0.0004429763648658991</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.00512966699898243</v>
+        <v>0.0001632803905522451</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.001347871031612158</v>
+        <v>0.0003351455670781434</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.002178697846829891</v>
+        <v>4.425649240147322e-05</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.007907826453447342</v>
+        <v>0.0003038259455934167</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.004379888065159321</v>
+        <v>0.000116593400889542</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.005292268935590982</v>
+        <v>0.0008371883304789662</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.003313856897875667</v>
+        <v>0.0002986405161209404</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.002864897018298507</v>
+        <v>0.0002803417155519128</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.003465691348537803</v>
+        <v>6.508538353955373e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.002487870398908854</v>
+        <v>0.0003158081381116062</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.001671903650276363</v>
+        <v>0.0001948567660292611</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.005201552994549274</v>
+        <v>0.0005370999570004642</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.001305847428739071</v>
+        <v>0.0003652375598903745</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.00425605196505785</v>
+        <v>0.0002064647851511836</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.0165798906236887</v>
+        <v>0.000861948705278337</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.002346593886613846</v>
+        <v>2.104387749568559e-05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.006343180313706398</v>
+        <v>0.001502570230513811</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.005703977774828672</v>
+        <v>8.715264266356826e-05</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0003756058868020773</v>
+        <v>0.001064162701368332</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0002968115732073784</v>
+        <v>0.0007047357503324747</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.002890982665121555</v>
+        <v>0.0002002540568355471</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.0005648656515404582</v>
+        <v>0.0003915848210453987</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.00300738075748086</v>
+        <v>8.281838381662965e-05</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.0009020823054015636</v>
+        <v>5.326539394445717e-05</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.008485578931868076</v>
+        <v>0.0001106151685235091</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.004741355776786804</v>
+        <v>0.0003359602415002882</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.00186455633956939</v>
+        <v>5.641287862090394e-05</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.0009331251494586468</v>
+        <v>0.0004151215543970466</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.004479401744902134</v>
+        <v>0.0008122404688037932</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.0004421737394295633</v>
+        <v>0.0001069363061105832</v>
       </c>
       <c r="DX12" t="n">
-        <v>5.208191851124866e-06</v>
+        <v>0.000288161973003298</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.007645980454981327</v>
+        <v>0.0007887760875746608</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.0003518943267408758</v>
+        <v>0.0003789069596678019</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.005600688513368368</v>
+        <v>4.604782952810638e-05</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.001040404895320535</v>
+        <v>0.0004073092713952065</v>
       </c>
       <c r="EC12" t="n">
-        <v>7.417402230203152e-06</v>
+        <v>0.0001131822500610724</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.0001091655867639929</v>
+        <v>0.0008048783056437969</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.003437376115471125</v>
+        <v>0.0006163667421787977</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.0004080620128661394</v>
+        <v>0.0003776149242185056</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.006056469399482012</v>
+        <v>0.0002022290282184258</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.003813945688307285</v>
+        <v>0.0003554713621269912</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.004707986023277044</v>
+        <v>0.000907967914827168</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.003410001285374165</v>
+        <v>0.0001117041538236663</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.003969352692365646</v>
+        <v>0.0001853203430073336</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.005034858826547861</v>
+        <v>4.900383646599948e-05</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0001902483199955896</v>
+        <v>7.497120532207191e-05</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.00170551729388535</v>
+        <v>4.593485209625214e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.001966556068509817</v>
+        <v>8.246760990004987e-05</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.007794935256242752</v>
+        <v>0.00051431282190606</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.0009181207278743386</v>
+        <v>9.743160626385361e-05</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.004822219721972942</v>
+        <v>0.0008372144075110555</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.002127046464011073</v>
+        <v>8.564582094550133e-05</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.008483070880174637</v>
+        <v>5.238806625129655e-05</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.005740197375416756</v>
+        <v>0.0002212453109677881</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.006370651070028543</v>
+        <v>0.0003936104767490178</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.0001642692368477583</v>
+        <v>0.0006191128632053733</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0005784820532426238</v>
+        <v>4.142116813454777e-05</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.007974413223564625</v>
+        <v>0.0004385524371173233</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.002299661282449961</v>
+        <v>5.957665416644886e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.005629262886941433</v>
+        <v>0.0009037768468260765</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.002398597542196512</v>
+        <v>8.750520646572113e-05</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.002273598918691278</v>
+        <v>0.0003128719399683177</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.003800481325015426</v>
+        <v>7.50176259316504e-05</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.001558005693368614</v>
+        <v>0.0003032593231182545</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.002853298326954246</v>
+        <v>6.301851681200787e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.000951200257986784</v>
+        <v>0.0002550882927607745</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.005293887108564377</v>
+        <v>0.0001759412116371095</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.003891411935910583</v>
+        <v>0.0002953955554403365</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.008607883006334305</v>
+        <v>0.0002452497428748757</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.002898088656365871</v>
+        <v>8.189433719962835e-05</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.001259165233932436</v>
+        <v>3.098437446169555e-05</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.002275252947583795</v>
+        <v>0.000250776793109253</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.0002553800004534423</v>
+        <v>0.0003182391228619963</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.002805490745231509</v>
+        <v>0.0003895345726050436</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.00483090290799737</v>
+        <v>0.0004152909386903048</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.003419077023863792</v>
+        <v>0.0005991813959553838</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.003221806604415178</v>
+        <v>0.0008537188405171037</v>
       </c>
       <c r="FS12" t="n">
-        <v>2.833548933267593e-05</v>
+        <v>0.0004540729278232902</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.001948604360222816</v>
+        <v>0.001355772488750517</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.0007845371728762984</v>
+        <v>0.0003048807848244905</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.005874591879546642</v>
+        <v>0.0006143047357909381</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.002859574276953936</v>
+        <v>0.001358116045594215</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.0008437912911176682</v>
+        <v>0.0002438439551042393</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.007464759051799774</v>
+        <v>0.0002183373435400426</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.002477217698469758</v>
+        <v>0.0001820579054765403</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.001944389077834785</v>
+        <v>0.0006471311789937317</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.0003293089102953672</v>
+        <v>0.0007102828822098672</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.0007968686986714602</v>
+        <v>0.0003304400306660682</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.003322306554764509</v>
+        <v>0.0008568807388655841</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.02002969011664391</v>
+        <v>0.0004448696854524314</v>
       </c>
       <c r="GF12" t="n">
-        <v>8.447674917988479e-05</v>
+        <v>0.0002039627579506487</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.002132543129846454</v>
+        <v>5.701325426343828e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1111776605248451</v>
+        <v>0.001104056951589882</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1788556277751923</v>
+        <v>0.01233592443168163</v>
       </c>
       <c r="C13" t="n">
-        <v>0.02018647082149982</v>
+        <v>0.002454107394441962</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1773834228515625</v>
+        <v>0.003266697749495506</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2904419004917145</v>
+        <v>0.005633134860545397</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5784560441970825</v>
+        <v>0.01216751150786877</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05909319967031479</v>
+        <v>0.002883721375837922</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3307327032089233</v>
+        <v>0.009261541068553925</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06615156680345535</v>
+        <v>0.002266884781420231</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0232103019952774</v>
+        <v>0.00215196143835783</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2331459224224091</v>
+        <v>0.01646550744771957</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05484979599714279</v>
+        <v>0.001264162361621857</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07954499125480652</v>
+        <v>0.00748535105958581</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1158952936530113</v>
+        <v>0.002460565883666277</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4547438025474548</v>
+        <v>0.01320541463792324</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0005823373794555664</v>
+        <v>0.00628581503406167</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2693929970264435</v>
+        <v>0.002535917330533266</v>
       </c>
       <c r="R13" t="n">
-        <v>0.008028700016438961</v>
+        <v>0.002197866328060627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03741037845611572</v>
+        <v>0.00165088102221489</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02809722162783146</v>
+        <v>0.003991370555013418</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001866698265075684</v>
+        <v>0.001497551100328565</v>
       </c>
       <c r="V13" t="n">
-        <v>0.02110203728079796</v>
+        <v>0.007617546245455742</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2038192600011826</v>
+        <v>0.005676675122231245</v>
       </c>
       <c r="X13" t="n">
-        <v>0.05930133536458015</v>
+        <v>0.002011424861848354</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.04115142673254013</v>
+        <v>0.001169375143945217</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.03396623581647873</v>
+        <v>0.002723087556660175</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.02015827596187592</v>
+        <v>0.0007590762688778341</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.00524333119392395</v>
+        <v>0.0005450398894026875</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.05603518337011337</v>
+        <v>0.003614763030782342</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0164311658591032</v>
+        <v>0.001536210416816175</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.04075076431035995</v>
+        <v>0.01087350212037563</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.02577841654419899</v>
+        <v>0.01328769978135824</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.04668644443154335</v>
+        <v>0.007415224332362413</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.04702901840209961</v>
+        <v>0.002945116488263011</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.07916082441806793</v>
+        <v>0.003975514322519302</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.02715052664279938</v>
+        <v>0.001718325074762106</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.003224147018045187</v>
+        <v>0.0002784808748401701</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01198383886367083</v>
+        <v>0.005574664566665888</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.028033297508955</v>
+        <v>0.001109410310164094</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.02600056864321232</v>
+        <v>0.003788453293964267</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.01372304186224937</v>
+        <v>0.003086500335484743</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01609869115054607</v>
+        <v>0.002755973022431135</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.004269905388355255</v>
+        <v>0.003321232041344047</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.06249431893229485</v>
+        <v>0.00678951246663928</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.009333716705441475</v>
+        <v>0.002303452463820577</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0449424684047699</v>
+        <v>0.002301653381437063</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.02636793069541454</v>
+        <v>0.02702474966645241</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.007624488323926926</v>
+        <v>0.0008866199059411883</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1967583000659943</v>
+        <v>0.005431449040770531</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.2801285684108734</v>
+        <v>0.0006637012120336294</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.334907054901123</v>
+        <v>0.008884130045771599</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.1034052520990372</v>
+        <v>0.00217967526987195</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.05359082296490669</v>
+        <v>0.002063052728772163</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.01638190262019634</v>
+        <v>0.0001370809623040259</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.07858112454414368</v>
+        <v>0.005117010325193405</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.09441696852445602</v>
+        <v>0.006830721162259579</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.03922457247972488</v>
+        <v>2.04907264560461e-05</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.1000464931130409</v>
+        <v>5.398760549724102e-06</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.02771057933568954</v>
+        <v>0.003437765873968601</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.06958845257759094</v>
+        <v>0.002557406900450587</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.05366044119000435</v>
+        <v>0.007760430686175823</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.1316929161548615</v>
+        <v>0.002557579893618822</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.02634782344102859</v>
+        <v>0.002492684405297041</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01846249029040337</v>
+        <v>0.003565038088709116</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0009388886392116547</v>
+        <v>0.002038822043687105</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.009124733507633209</v>
+        <v>0.001076913322322071</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.1758664697408676</v>
+        <v>0.002985066967085004</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.07981592416763306</v>
+        <v>0.0008587960619479418</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.02206047065556049</v>
+        <v>0.0005487872404046357</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.001669518649578094</v>
+        <v>0.006081818602979183</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.1159317344427109</v>
+        <v>0.004918050952255726</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.03520673885941505</v>
+        <v>0.001820834702812135</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.000428813393227756</v>
+        <v>0.004515786189585924</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.04878279194235802</v>
+        <v>0.01342255435883999</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.01718898490071297</v>
+        <v>0.002369976369664073</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.1465222090482712</v>
+        <v>0.006745569407939911</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1288622170686722</v>
+        <v>0.001743586268275976</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.2818129658699036</v>
+        <v>0.009262588806450367</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.08241294324398041</v>
+        <v>0.001561653451062739</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.002141095697879791</v>
+        <v>0.001353449071757495</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.02675537765026093</v>
+        <v>0.002193056046962738</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.01566006615757942</v>
+        <v>0.001288703875616193</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.009741934016346931</v>
+        <v>0.004207245539873838</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.01814173720777035</v>
+        <v>0.001189464819617569</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.007756500504910946</v>
+        <v>0.00186698033940047</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.07310076802968979</v>
+        <v>0.0005506947636604309</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.1014757379889488</v>
+        <v>0.003705709939822555</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.03931902348995209</v>
+        <v>0.001561936340294778</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.06160562485456467</v>
+        <v>0.003044853685423732</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0007155211642384529</v>
+        <v>0.0006355951773002744</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.001201932784169912</v>
+        <v>0.004265911411494017</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.09300962090492249</v>
+        <v>0.01294509042054415</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.04351157695055008</v>
+        <v>0.0004249174962751567</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.1121808886528015</v>
+        <v>7.063453085720539e-05</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.1231282874941826</v>
+        <v>0.01045152358710766</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0548018217086792</v>
+        <v>0.006415468640625477</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.09785734862089157</v>
+        <v>0.002508813980966806</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.1256791353225708</v>
+        <v>0.00345417158678174</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.01181637495756149</v>
+        <v>0.00412991177290678</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.01814322918653488</v>
+        <v>0.002437453018501401</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01667463034391403</v>
+        <v>0.003866426413878798</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01554268598556519</v>
+        <v>0.0007465892122127116</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.0006055999547243118</v>
+        <v>0.001315106404945254</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.06248023733496666</v>
+        <v>0.001224953914061189</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.1104664131999016</v>
+        <v>0.003087666817009449</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.01761427521705627</v>
+        <v>0.0008671486284583807</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.04990209639072418</v>
+        <v>0.00243422482162714</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.02353446930646896</v>
+        <v>0.001051993109285831</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.119187705218792</v>
+        <v>0.002513620536774397</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.02197294123470783</v>
+        <v>0.001638617133721709</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.01650748029351234</v>
+        <v>0.002301557455211878</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.2032175958156586</v>
+        <v>0.002722070785239339</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01389596424996853</v>
+        <v>0.006106036715209484</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.076453797519207</v>
+        <v>0.001904893899336457</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.07773500680923462</v>
+        <v>0.001026873593218625</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.06464033573865891</v>
+        <v>0.003914628177881241</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.08796071261167526</v>
+        <v>0.003077133093029261</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.09116615355014801</v>
+        <v>0.0001977987412828952</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.06128215044736862</v>
+        <v>0.002999274991452694</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.02864126116037369</v>
+        <v>0.0003623501979745924</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.02662687189877033</v>
+        <v>0.007900606840848923</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.1099256277084351</v>
+        <v>0.002440760144963861</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.1394904255867004</v>
+        <v>0.005187899805605412</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.1003552824258804</v>
+        <v>0.0008304170914925635</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.03024208173155785</v>
+        <v>0.0005033884663134813</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.03339075297117233</v>
+        <v>0.004007860086858273</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.01014536060392857</v>
+        <v>0.0001990465680137277</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.06766190379858017</v>
+        <v>0.001165057416073978</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.03981428220868111</v>
+        <v>0.0007090603467077017</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.079486183822155</v>
+        <v>0.001202329993247986</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.1087222918868065</v>
+        <v>0.000630857131909579</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.08759185671806335</v>
+        <v>0.004139233380556107</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0401405543088913</v>
+        <v>0.002888092771172523</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0252983532845974</v>
+        <v>0.0009200642816722393</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.04376617074012756</v>
+        <v>0.003671081503853202</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.001302042044699192</v>
+        <v>0.001266065053641796</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.06140942871570587</v>
+        <v>0.0003313599736429751</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.04842929914593697</v>
+        <v>0.001122538582421839</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.08239691704511642</v>
+        <v>0.004388542380183935</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.06350916624069214</v>
+        <v>0.002489917445927858</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.07962847501039505</v>
+        <v>8.974602678790689e-05</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0157674066722393</v>
+        <v>0.000931614194996655</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.03976356238126755</v>
+        <v>0.001273645088076591</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.01502716261893511</v>
+        <v>0.0004639000399038196</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.05655040219426155</v>
+        <v>0.002573490841314197</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.01381952967494726</v>
+        <v>0.0003677177592180669</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.002400103956460953</v>
+        <v>0.003205940360203385</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.05328574031591415</v>
+        <v>0.0005594028043560684</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.07539591193199158</v>
+        <v>0.001067617442458868</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.008698214776813984</v>
+        <v>0.002164827194064856</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.005520639941096306</v>
+        <v>0.002882496686652303</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.2077625542879105</v>
+        <v>0.003297109389677644</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.03540945425629616</v>
+        <v>0.002754683140665293</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.02965064533054829</v>
+        <v>0.001884886296465993</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.013354467228055</v>
+        <v>0.004762073047459126</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.005992056801915169</v>
+        <v>0.001747895497828722</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.01365005318075418</v>
+        <v>0.001937512890435755</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.07957457005977631</v>
+        <v>0.001282945508137345</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.09308616816997528</v>
+        <v>0.003636231645941734</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.04201222583651543</v>
+        <v>0.001857934286817908</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.06601253151893616</v>
+        <v>0.002840598579496145</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.01375732943415642</v>
+        <v>0.001464419183321297</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.05240897089242935</v>
+        <v>0.003455062629655004</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01178768463432789</v>
+        <v>0.006926074624061584</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.002388998866081238</v>
+        <v>0.0006539398455061018</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.1690639555454254</v>
+        <v>0.003899128641933203</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0623546801507473</v>
+        <v>0.002924332860857248</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02405068837106228</v>
+        <v>0.004267294425517321</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.02989671751856804</v>
+        <v>0.004623756278306246</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.01316838152706623</v>
+        <v>0.004329800140112638</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.02736884169280529</v>
+        <v>0.000387227104511112</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.02698591724038124</v>
+        <v>0.001697957748547196</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.2097582519054413</v>
+        <v>0.01159661449491978</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.04428930208086967</v>
+        <v>0.002926079789176583</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.06875447928905487</v>
+        <v>0.003174923593178391</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.3382295966148376</v>
+        <v>0.002232362749055028</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.08765574544668198</v>
+        <v>0.000626609253231436</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.07875333726406097</v>
+        <v>0.00514649786055088</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.1988891065120697</v>
+        <v>0.001951009733602405</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.07378125935792923</v>
+        <v>0.002167222322896123</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.04492758214473724</v>
+        <v>0.001064954674802721</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.1123899668455124</v>
+        <v>0.001943079754710197</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.01185517758131027</v>
+        <v>0.00263450900092721</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0475667305290699</v>
+        <v>0.004113887436687946</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.1192051023244858</v>
+        <v>0.0002913745120167732</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.03601327538490295</v>
+        <v>0.0003586072707548738</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.07133083045482635</v>
+        <v>0.001659357687458396</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.05392304807901382</v>
+        <v>0.002444133628159761</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0348869301378727</v>
+        <v>0.002523980801925063</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.01498351618647575</v>
+        <v>0.0230913981795311</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002148165833204985</v>
+        <v>0.02276952005922794</v>
       </c>
       <c r="C14" t="n">
-        <v>0.003295943839475513</v>
+        <v>0.007253140211105347</v>
       </c>
       <c r="D14" t="n">
-        <v>0.007507950067520142</v>
+        <v>0.1194066256284714</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00186725496314466</v>
+        <v>0.04824506491422653</v>
       </c>
       <c r="F14" t="n">
-        <v>0.003660753602162004</v>
+        <v>0.0211506076157093</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001839630189351737</v>
+        <v>0.03898641839623451</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001032522413879633</v>
+        <v>0.001923795323818922</v>
       </c>
       <c r="I14" t="n">
-        <v>7.068563718348742e-05</v>
+        <v>0.02829944714903831</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01261492818593979</v>
+        <v>0.01561656314879656</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0005179969593882561</v>
+        <v>0.006485260557383299</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003775679273530841</v>
+        <v>0.004220077767968178</v>
       </c>
       <c r="M14" t="n">
-        <v>0.002406617626547813</v>
+        <v>0.1576014906167984</v>
       </c>
       <c r="N14" t="n">
-        <v>0.003292302368208766</v>
+        <v>0.02200720831751823</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0006213742890395224</v>
+        <v>0.05040743947029114</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001155755016952753</v>
+        <v>0.04348423331975937</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.002025766763836145</v>
+        <v>0.03421561419963837</v>
       </c>
       <c r="R14" t="n">
-        <v>0.001182246604003012</v>
+        <v>0.02134972251951694</v>
       </c>
       <c r="S14" t="n">
-        <v>0.002022573258727789</v>
+        <v>0.001829470042139292</v>
       </c>
       <c r="T14" t="n">
-        <v>0.00287601794116199</v>
+        <v>0.0001682261936366558</v>
       </c>
       <c r="U14" t="n">
-        <v>0.001236208016052842</v>
+        <v>0.003652488347142935</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0001122998655773699</v>
+        <v>0.01498794928193092</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0017426663544029</v>
+        <v>0.00739633571356535</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0006343333516269922</v>
+        <v>0.02437842264771461</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.0001172967749880627</v>
+        <v>0.003996007144451141</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.002072283765301108</v>
+        <v>0.003304251469671726</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0003341127885505557</v>
+        <v>0.005270030349493027</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.001302684075199068</v>
+        <v>0.01039923168718815</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.002510215388610959</v>
+        <v>0.02047791704535484</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.001055342145264149</v>
+        <v>0.001626993645913899</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0008625262416899204</v>
+        <v>0.003238098230212927</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.001856275484897196</v>
+        <v>0.0124433021992445</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.0001866686507128179</v>
+        <v>0.01219064556062222</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0004629477625712752</v>
+        <v>0.0110043752938509</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0009156452142633498</v>
+        <v>0.02061991393566132</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0009876564145088196</v>
+        <v>0.02622572332620621</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.001534686423838139</v>
+        <v>0.0065709981136024</v>
       </c>
       <c r="AL14" t="n">
-        <v>6.469065556302667e-05</v>
+        <v>0.01727142184972763</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0005602175369858742</v>
+        <v>0.005163324996829033</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.001327539677731693</v>
+        <v>0.02619650587439537</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.001344507676549256</v>
+        <v>0.01643064059317112</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.0006801409181207418</v>
+        <v>0.01684014685451984</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.001516665099188685</v>
+        <v>0.02210674993693829</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.001330648316070437</v>
+        <v>2.01839575311169e-05</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.0004782371106557548</v>
+        <v>0.007260004989802837</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.008721898309886456</v>
+        <v>0.01165917702019215</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.002278452971950173</v>
+        <v>0.01204472035169601</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.003340673632919788</v>
+        <v>0.01476359833031893</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.004011296201497316</v>
+        <v>0.07884722948074341</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.002473466796800494</v>
+        <v>0.03773175179958344</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0005228561349213123</v>
+        <v>0.01116592809557915</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.001173345372080803</v>
+        <v>0.003095531370490789</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.003290706779807806</v>
+        <v>0.02114144712686539</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.001057951711118221</v>
+        <v>0.001884758472442627</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.005920558236539364</v>
+        <v>0.02626898884773254</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.006710988469421864</v>
+        <v>0.01063893083482981</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.0007154279155656695</v>
+        <v>0.007098381407558918</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0003122073539998382</v>
+        <v>0.02386896125972271</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.002030003350228071</v>
+        <v>0.02888282760977745</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.0001558154472149909</v>
+        <v>0.01097872573882341</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.0002894042117986828</v>
+        <v>0.01974279247224331</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.003508773865178227</v>
+        <v>0.009394969791173935</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.002436705632135272</v>
+        <v>0.05062867701053619</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.0005904376739636064</v>
+        <v>0.007277369499206543</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.003638595808297396</v>
+        <v>0.01378924772143364</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0007760211592540145</v>
+        <v>0.0040611089207232</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0002997236442752182</v>
+        <v>0.009609127417206764</v>
       </c>
       <c r="BP14" t="n">
-        <v>1.411652192473412e-05</v>
+        <v>0.02946192026138306</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.001629211939871311</v>
+        <v>0.0114109804853797</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.001220501959323883</v>
+        <v>0.005436021368950605</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.0004475079185795039</v>
+        <v>0.01365893613547087</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.001309648039750755</v>
+        <v>0.01281808409839869</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.004074693191796541</v>
+        <v>0.006083141546696424</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.0006979366298764944</v>
+        <v>0.003641907591372728</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.001237298361957073</v>
+        <v>0.001262913458049297</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.001368642668239772</v>
+        <v>0.06899543106555939</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0006113479612395167</v>
+        <v>0.0114047285169363</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.0006649612332694232</v>
+        <v>0.0186382420361042</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.000150150794070214</v>
+        <v>0.004543725401163101</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.002496878383681178</v>
+        <v>0.006552034057676792</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0007147159776650369</v>
+        <v>0.01223853509873152</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.002787101315334439</v>
+        <v>0.008034661412239075</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.002064452972263098</v>
+        <v>0.01407788414508104</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0001044087402988225</v>
+        <v>0.001452230615541339</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.0004886342212557793</v>
+        <v>0.04209421202540398</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.0001396241714246571</v>
+        <v>0.008038856089115143</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.002107577864080667</v>
+        <v>0.0160006545484066</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0002207697252742946</v>
+        <v>0.0008686852524988353</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.001613640459254384</v>
+        <v>0.01630260981619358</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.0004029186966363341</v>
+        <v>0.006003950722515583</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.003074428997933865</v>
+        <v>0.004351446870714426</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.001828018575906754</v>
+        <v>0.02498330920934677</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0003775909135583788</v>
+        <v>0.01585382781922817</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.002875773468986154</v>
+        <v>0.06416650116443634</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.003839779645204544</v>
+        <v>0.03629966452717781</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.00102521013468504</v>
+        <v>0.02243739180266857</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.002687644213438034</v>
+        <v>0.0003463858738541603</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.005123015027493238</v>
+        <v>0.02666020020842552</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.0009712214814499021</v>
+        <v>0.0236709825694561</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.002301248023286462</v>
+        <v>0.005656105000525713</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.002343607367947698</v>
+        <v>0.01286503486335278</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0003274336049798876</v>
+        <v>0.004225180018693209</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0006561597110703588</v>
+        <v>0.04539205133914948</v>
       </c>
       <c r="CZ14" t="n">
-        <v>3.135013685096055e-05</v>
+        <v>0.003462150460109115</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.001786581473425031</v>
+        <v>0.01047512609511614</v>
       </c>
       <c r="DB14" t="n">
-        <v>8.72655218699947e-05</v>
+        <v>0.004979971330612898</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.00124637596309185</v>
+        <v>0.01509479619562626</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.0003737612860277295</v>
+        <v>0.002202194184064865</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.001339819864369929</v>
+        <v>0.0008901613764464855</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.002869503339752555</v>
+        <v>0.02218238264322281</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.003039102535694838</v>
+        <v>6.536953151226044e-06</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.004743214696645737</v>
+        <v>0.03141047060489655</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.00184707879088819</v>
+        <v>0.01310739759355783</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.001477038720622659</v>
+        <v>0.02401917241513729</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.002129394793882966</v>
+        <v>0.007535312324762344</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.005051671527326107</v>
+        <v>0.05469677224755287</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.001057746121659875</v>
+        <v>0.001097310334444046</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.001832555513828993</v>
+        <v>0.006095807068049908</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.000308023823890835</v>
+        <v>0.01655026525259018</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0008535537635907531</v>
+        <v>0.02975117415189743</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.001978315412998199</v>
+        <v>0.01821398362517357</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.00320722977630794</v>
+        <v>0.007580983452498913</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.001415767008438706</v>
+        <v>0.01511342078447342</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0008924821158871055</v>
+        <v>0.01322454120963812</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.0004381034232210368</v>
+        <v>0.002787483856081963</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.00137159030418843</v>
+        <v>0.02782008983194828</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.002178646624088287</v>
+        <v>0.001115138176828623</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.0009568891255185008</v>
+        <v>0.005664916709065437</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.0003403429873287678</v>
+        <v>0.05060804635286331</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.001230731257237494</v>
+        <v>0.01490484736859798</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.001816928968764842</v>
+        <v>0.005939343944191933</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0002000277308980003</v>
+        <v>0.01531326584517956</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.000871100986842066</v>
+        <v>0.007364718243479729</v>
       </c>
       <c r="ED14" t="n">
-        <v>1.979794615181163e-05</v>
+        <v>0.04843445867300034</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.0004834043502341956</v>
+        <v>0.02884341590106487</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.003075314685702324</v>
+        <v>0.02785902470350266</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.00348758464679122</v>
+        <v>0.001715367776341736</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.002054548822343349</v>
+        <v>0.001768654910847545</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.002940125530585647</v>
+        <v>0.04013814404606819</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.002927478868514299</v>
+        <v>0.003831707406789064</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.001058828784152865</v>
+        <v>0.0212435144931078</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0003340833354741335</v>
+        <v>0.002536166459321976</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0004687995533458889</v>
+        <v>0.00948475394397974</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.00020153250079602</v>
+        <v>0.0003628171980381012</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0002865162095986307</v>
+        <v>0.00957382470369339</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.004153474699705839</v>
+        <v>0.01936183869838715</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.000759979069698602</v>
+        <v>0.01116526033729315</v>
       </c>
       <c r="ER14" t="n">
-        <v>9.094971755985171e-05</v>
+        <v>0.03790194541215897</v>
       </c>
       <c r="ES14" t="n">
-        <v>5.724071525037289e-05</v>
+        <v>0.004783593583852053</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.002605955582112074</v>
+        <v>0.02844275906682014</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.0009386548190377653</v>
+        <v>0.01682658493518829</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.0005772453150711954</v>
+        <v>0.0164951179176569</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.002538193482905626</v>
+        <v>0.02123879082500935</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.002373373601585627</v>
+        <v>0.004961149301379919</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.002388026099652052</v>
+        <v>0.008907029405236244</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0006559423636645079</v>
+        <v>0.00186924752779305</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0007299806457012892</v>
+        <v>0.05108925700187683</v>
       </c>
       <c r="FB14" t="n">
-        <v>4.096886186744086e-05</v>
+        <v>0.005965564399957657</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.001722993212752044</v>
+        <v>0.008865396492183208</v>
       </c>
       <c r="FD14" t="n">
-        <v>3.995923907496035e-05</v>
+        <v>0.004941707011312246</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.001476152916438878</v>
+        <v>0.01811107620596886</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0004267790936864913</v>
+        <v>0.002835073973983526</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.0005354948807507753</v>
+        <v>0.00148311723023653</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.00224863039329648</v>
+        <v>0.003107058582827449</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.002797908149659634</v>
+        <v>0.002634796546772122</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0009667464764788747</v>
+        <v>0.02058642730116844</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.001240635756403208</v>
+        <v>0.03374380618333817</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.0026305066421628</v>
+        <v>0.01547602564096451</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.001993016339838505</v>
+        <v>0.005632372573018074</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0009186214301735163</v>
+        <v>0.01942391507327557</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0008285582298412919</v>
+        <v>0.009518876671791077</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.002163626253604889</v>
+        <v>0.02571114711463451</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0008542940486222506</v>
+        <v>0.04463933035731316</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.002448670566082001</v>
+        <v>0.003304331796243787</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.00199350924231112</v>
+        <v>0.05022327974438667</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.002972509246319532</v>
+        <v>0.01140941865742207</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.003275701310485601</v>
+        <v>0.02874094247817993</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.002241011941805482</v>
+        <v>0.006094553507864475</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.0001711393124423921</v>
+        <v>0.03753284364938736</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.0004623163840733469</v>
+        <v>0.01302273571491241</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.001058192690834403</v>
+        <v>0.007480546832084656</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0001562847755849361</v>
+        <v>0.01934518665075302</v>
       </c>
       <c r="GA14" t="n">
-        <v>4.734264803119004e-05</v>
+        <v>0.01043848786503077</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0001799581805244088</v>
+        <v>0.04707740247249603</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.002026491099968553</v>
+        <v>0.01146683190017939</v>
       </c>
       <c r="GD14" t="n">
-        <v>7.068942068144679e-05</v>
+        <v>0.01520987972617149</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.001501339487731457</v>
+        <v>0.03320034220814705</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.0006484707118943334</v>
+        <v>0.01846292242407799</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.001010758453048766</v>
+        <v>0.002704310696572065</v>
       </c>
     </row>
     <row r="15">
@@ -9534,1140 +9534,1140 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.001266939449124038</v>
+        <v>8.521775498593342e-07</v>
       </c>
       <c r="B17" t="n">
-        <v>0.008021142333745956</v>
+        <v>3.882682449329877e-06</v>
       </c>
       <c r="C17" t="n">
-        <v>0.001157720922492445</v>
+        <v>6.734778708050726e-07</v>
       </c>
       <c r="D17" t="n">
-        <v>0.006249427329748869</v>
+        <v>4.139636530453572e-06</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002233721083030105</v>
+        <v>5.563950367104553e-08</v>
       </c>
       <c r="F17" t="n">
-        <v>0.002223899122327566</v>
+        <v>2.857947947632056e-06</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003666845732368529</v>
+        <v>9.941832104232162e-07</v>
       </c>
       <c r="H17" t="n">
-        <v>9.167198732029647e-05</v>
+        <v>1.302045916418137e-06</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000783928029704839</v>
+        <v>2.416371387425897e-07</v>
       </c>
       <c r="J17" t="n">
-        <v>0.002913497854024172</v>
+        <v>2.72684019364533e-07</v>
       </c>
       <c r="K17" t="n">
-        <v>0.006081214174628258</v>
+        <v>4.344739863881841e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0007358338916674256</v>
+        <v>9.701716408017091e-07</v>
       </c>
       <c r="M17" t="n">
-        <v>0.005282886791974306</v>
+        <v>5.218547812546603e-06</v>
       </c>
       <c r="N17" t="n">
-        <v>0.003350628772750497</v>
+        <v>1.815061523302575e-06</v>
       </c>
       <c r="O17" t="n">
-        <v>0.003789861919358373</v>
+        <v>2.923367219409556e-06</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0009934389963746071</v>
+        <v>5.866465926374076e-07</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.00079352903412655</v>
+        <v>2.895809245728742e-07</v>
       </c>
       <c r="R17" t="n">
-        <v>6.10425413469784e-05</v>
+        <v>9.637989961674975e-08</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0007733739912509918</v>
+        <v>2.073500695587427e-07</v>
       </c>
       <c r="T17" t="n">
-        <v>0.001307504717260599</v>
+        <v>1.524023218735238e-07</v>
       </c>
       <c r="U17" t="n">
-        <v>0.001327542820945382</v>
+        <v>2.971714536670333e-07</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0006900159060023725</v>
+        <v>5.113964789416059e-07</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0009300451492890716</v>
+        <v>1.102877035918937e-06</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0007993885083124042</v>
+        <v>1.120560568779183e-06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.001343919080682099</v>
+        <v>1.009762854664586e-06</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.001384951989166439</v>
+        <v>8.829462103676633e-07</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.001571489730849862</v>
+        <v>1.255705797120754e-07</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0008880567620508373</v>
+        <v>7.535340529329915e-08</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.0007343297475017607</v>
+        <v>6.089393878028204e-08</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.000191197352251038</v>
+        <v>1.569969754200429e-07</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.0008970134658738971</v>
+        <v>1.280635501643701e-06</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.000249485980020836</v>
+        <v>2.363247801895341e-07</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.0001354643463855609</v>
+        <v>1.165307367045898e-06</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.000707860104739666</v>
+        <v>5.676772616425296e-07</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0002035453944699839</v>
+        <v>1.442324673917028e-06</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.0004514953179750592</v>
+        <v>5.747209002038289e-07</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.0008671206887811422</v>
+        <v>3.994983046595735e-07</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.001284089288674295</v>
+        <v>9.108046583605756e-07</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.017568865790963e-05</v>
+        <v>2.297516061844362e-07</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.0001221008569700643</v>
+        <v>1.616289978301211e-06</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.0004265432071406394</v>
+        <v>3.460919515418936e-07</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.737233393825591e-05</v>
+        <v>4.263770279067103e-07</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.0003820297424681485</v>
+        <v>1.212781910453486e-07</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0003150840639136732</v>
+        <v>5.066008839094138e-07</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0009948826627805829</v>
+        <v>3.52506873468883e-07</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.000637071905657649</v>
+        <v>3.043009257908125e-07</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.005880283191800117</v>
+        <v>3.525398369674804e-06</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.000103872298495844</v>
+        <v>1.000662905425997e-06</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.002046620240435004</v>
+        <v>1.348635237263807e-06</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.001140221953392029</v>
+        <v>2.14829265132721e-06</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.000842100998852402</v>
+        <v>1.748005956869747e-06</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.0006203430239111185</v>
+        <v>8.935298012602289e-08</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.0009553334675729275</v>
+        <v>5.594424834498568e-08</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.001636581378988922</v>
+        <v>9.1304934812797e-07</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.001023299992084503</v>
+        <v>8.560927255985007e-08</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.001427212497219443</v>
+        <v>5.001768954571162e-07</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.002810209058225155</v>
+        <v>6.350440457936202e-07</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.001235097995959222</v>
+        <v>4.198405463284871e-07</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.00227244128473103</v>
+        <v>1.830664245972002e-06</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.001958935521543026</v>
+        <v>4.056665829921258e-07</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.0006346894078887999</v>
+        <v>1.707888088731124e-07</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.0008600367000326514</v>
+        <v>7.383561637652747e-07</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.906894875806756e-05</v>
+        <v>3.956638465751894e-07</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.0008544953307136893</v>
+        <v>5.216558207621347e-08</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.002186520723626018</v>
+        <v>6.648763246630551e-07</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.001995038473978639</v>
+        <v>7.323035333683947e-08</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0001984691916732118</v>
+        <v>9.525991799819167e-07</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.001368378521874547</v>
+        <v>7.622241469107394e-07</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.0004719884600490332</v>
+        <v>4.908854407403851e-07</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.0006252186140045524</v>
+        <v>2.151128626337595e-07</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.0008865296258591115</v>
+        <v>3.308327052309323e-07</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0007419474422931671</v>
+        <v>4.201770309464337e-08</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.0002740461495704949</v>
+        <v>6.007476116565158e-08</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.002810553414747119</v>
+        <v>2.355951210120111e-06</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.00182358780875802</v>
+        <v>4.634362653632706e-07</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.001511014415882528</v>
+        <v>1.767579988154466e-06</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.0003577616007532924</v>
+        <v>1.833346061630436e-07</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.654109943658113e-05</v>
+        <v>1.591262503097823e-06</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.0006784198340028524</v>
+        <v>1.023775780595315e-06</v>
       </c>
       <c r="CB17" t="n">
-        <v>6.058876169845462e-05</v>
+        <v>1.432314604699059e-07</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.001396272564306855</v>
+        <v>1.505344897623218e-07</v>
       </c>
       <c r="CD17" t="n">
-        <v>8.357345359399915e-05</v>
+        <v>1.002350487055992e-07</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.00100224930793047</v>
+        <v>1.280536594094883e-06</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.001299932831898332</v>
+        <v>1.497792823101918e-07</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.0005462688859552145</v>
+        <v>1.307023467234103e-06</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.0001345392811344936</v>
+        <v>8.652334315684129e-08</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.0006938225124031305</v>
+        <v>4.29808778790175e-07</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.000224808492930606</v>
+        <v>2.113014545557235e-07</v>
       </c>
       <c r="CK17" t="n">
-        <v>6.401423888746649e-05</v>
+        <v>2.802727863127075e-07</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.0007723882445134223</v>
+        <v>7.972268889488987e-08</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.001409603864885867</v>
+        <v>8.623775329397176e-07</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.0004916208563372493</v>
+        <v>1.977678266484872e-06</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.0006797648966312408</v>
+        <v>1.281410163755936e-06</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.001954205567017198</v>
+        <v>1.125046310335165e-06</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.0008557087276130915</v>
+        <v>3.467291662673233e-07</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.001437274389900267</v>
+        <v>3.037707756448071e-07</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.001127854338847101</v>
+        <v>3.545637241586519e-07</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.0002748327679000795</v>
+        <v>3.881141026340629e-07</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.0007723894668743014</v>
+        <v>1.614637312741252e-07</v>
       </c>
       <c r="CV17" t="n">
-        <v>7.261969585670158e-05</v>
+        <v>2.206116000991187e-08</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.0009489783551543951</v>
+        <v>1.230565203513834e-06</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.001178821199573576</v>
+        <v>3.134810242499952e-07</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.0009624339290894568</v>
+        <v>1.383312451253005e-06</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.0004499189089983702</v>
+        <v>3.744578691566858e-07</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.0007540850201621652</v>
+        <v>4.584584587519203e-07</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.0003714761114679277</v>
+        <v>2.274181269967812e-07</v>
       </c>
       <c r="DC17" t="n">
-        <v>9.500369924353436e-05</v>
+        <v>3.456287629433064e-07</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.0004428964457474649</v>
+        <v>1.154088593580127e-07</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.001352474093437195</v>
+        <v>4.568474025745672e-07</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.0006529043894261122</v>
+        <v>1.4005335060574e-06</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.0003527023072820157</v>
+        <v>4.558000910037663e-08</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.003270168788731098</v>
+        <v>1.179212063107116e-06</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.00182432634755969</v>
+        <v>5.107115157443332e-07</v>
       </c>
       <c r="DJ17" t="n">
-        <v>4.025328962597996e-06</v>
+        <v>1.542330892334576e-06</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.0004180817340966314</v>
+        <v>1.28480451166979e-07</v>
       </c>
       <c r="DL17" t="n">
-        <v>9.55056311795488e-05</v>
+        <v>2.312475771759637e-06</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.0005036810762248933</v>
+        <v>4.997143605578458e-07</v>
       </c>
       <c r="DN17" t="n">
-        <v>4.625300061888993e-05</v>
+        <v>9.896209007820289e-08</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.0002623539767228067</v>
+        <v>9.445167279409361e-07</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.0009497630526311696</v>
+        <v>2.967165642075997e-07</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.0002039155078819022</v>
+        <v>4.76006306371346e-07</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.118106052279472e-06</v>
+        <v>4.402840261263918e-07</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0002411433670204133</v>
+        <v>4.570162559502933e-07</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.0001738876744639128</v>
+        <v>9.580586493029841e-07</v>
       </c>
       <c r="DU17" t="n">
-        <v>8.666288340464234e-05</v>
+        <v>7.025909098956618e-07</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.0006297408835962415</v>
+        <v>8.555377348784532e-07</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.0003536776930559427</v>
+        <v>2.19119300481907e-08</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.001614309498108923</v>
+        <v>4.12544665095993e-07</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.001053091138601303</v>
+        <v>9.773025340109598e-07</v>
       </c>
       <c r="DZ17" t="n">
-        <v>2.931990457000211e-05</v>
+        <v>8.325547469212324e-07</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.0001780217280611396</v>
+        <v>8.680010523676174e-07</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.0005003723199479282</v>
+        <v>7.053186834582448e-08</v>
       </c>
       <c r="EC17" t="n">
-        <v>5.984904419165105e-05</v>
+        <v>2.558316509748693e-07</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0002606809139251709</v>
+        <v>1.574232669554476e-06</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.000972526497207582</v>
+        <v>1.471969312660804e-06</v>
       </c>
       <c r="EF17" t="n">
-        <v>3.424246096983552e-05</v>
+        <v>7.708990779065061e-09</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.0004685170424636453</v>
+        <v>6.057564405637095e-07</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.0008528121979907155</v>
+        <v>4.096485781701631e-07</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.0004379218444228172</v>
+        <v>8.323307838509209e-07</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.0002827784919645637</v>
+        <v>5.73962097405456e-07</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.0004401489568408579</v>
+        <v>3.760097797567141e-07</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.0006119979079812765</v>
+        <v>2.646100369929627e-07</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.0005125970928929746</v>
+        <v>1.726726424067238e-07</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.0001011101412586868</v>
+        <v>6.228247428907707e-08</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.0002131505752913654</v>
+        <v>1.212792426485976e-07</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.0003281323006376624</v>
+        <v>7.690734378229536e-07</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.001357416971586645</v>
+        <v>3.52680615378631e-07</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.0002975130046252161</v>
+        <v>8.624400607004645e-07</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.001098712789826095</v>
+        <v>9.892223715723958e-07</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.0006599570042453706</v>
+        <v>7.745621033450334e-09</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.0006240667426027358</v>
+        <v>3.352024009473098e-07</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.001561387558467686</v>
+        <v>7.775062726977922e-07</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.0004827400844078511</v>
+        <v>7.052283308439655e-07</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.000190266888239421</v>
+        <v>5.604587016705409e-09</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.0008714887080714107</v>
+        <v>1.380693447572412e-06</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.001076492946594954</v>
+        <v>2.159041798677208e-07</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.0006654210155829787</v>
+        <v>1.513535721642256e-06</v>
       </c>
       <c r="FB17" t="n">
-        <v>9.726292046252638e-05</v>
+        <v>8.322377453851004e-08</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.0007438994362019002</v>
+        <v>4.867837901656458e-07</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.0005526526365429163</v>
+        <v>5.205375686045954e-08</v>
       </c>
       <c r="FE17" t="n">
-        <v>9.821353887673467e-05</v>
+        <v>4.611603401372122e-07</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.0009383794385939837</v>
+        <v>8.91470151032081e-08</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.000634742493275553</v>
+        <v>7.517510880461487e-08</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.0006149575929157436</v>
+        <v>6.232890541468805e-07</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.001065024640411139</v>
+        <v>7.658725280634826e-07</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.00131216470617801</v>
+        <v>8.774275102041429e-07</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.0002204469492426142</v>
+        <v>4.779259299425576e-08</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.001154640689492226</v>
+        <v>4.402861293328897e-07</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.0001006154634524137</v>
+        <v>2.134443093382288e-07</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.001177033875137568</v>
+        <v>6.26266043468604e-08</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.001717468025162816</v>
+        <v>7.918788469396532e-07</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.0003612994914874434</v>
+        <v>1.690512590357685e-06</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.0003969133831560612</v>
+        <v>1.56497787884291e-06</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.0006000465946272016</v>
+        <v>5.681895345333032e-07</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.001019633840769529</v>
+        <v>8.544515708308609e-07</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.00138437794521451</v>
+        <v>1.043849238158145e-06</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.0001504724496044219</v>
+        <v>4.082438067598559e-07</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.001107563497498631</v>
+        <v>6.372994221237605e-07</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.001029874430969357</v>
+        <v>7.830641379769077e-07</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.001105669536627829</v>
+        <v>1.368747177821206e-07</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.002110308036208153</v>
+        <v>5.34123671513953e-07</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.0004839561297558248</v>
+        <v>3.239782131458924e-07</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.0001702836452750489</v>
+        <v>1.175322267954471e-06</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.000364171399269253</v>
+        <v>7.976149163368973e-07</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.001728493021801114</v>
+        <v>1.122049752666499e-06</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.0006837746477685869</v>
+        <v>1.060224349203054e-06</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.003008571686223149</v>
+        <v>1.66965742209868e-06</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.0002341753279324621</v>
+        <v>3.432672031067341e-07</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.0004283994494471699</v>
+        <v>8.911536042432999e-08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.002059884835034609</v>
+        <v>0.0003833766095340252</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01837487518787384</v>
+        <v>0.0004241689457558095</v>
       </c>
       <c r="C18" t="n">
-        <v>0.002967819105833769</v>
+        <v>0.001515406649559736</v>
       </c>
       <c r="D18" t="n">
-        <v>0.008341768756508827</v>
+        <v>0.000417497445596382</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00430197874084115</v>
+        <v>0.0005253531271591783</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02689640037715435</v>
+        <v>0.002123563084751368</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005516376346349716</v>
+        <v>0.0005753003060817719</v>
       </c>
       <c r="H18" t="n">
-        <v>0.009041010402143002</v>
+        <v>0.0006055566482245922</v>
       </c>
       <c r="I18" t="n">
-        <v>0.004092314280569553</v>
+        <v>4.841271584155038e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.004785963799804449</v>
+        <v>5.761906504631042e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01214139815419912</v>
+        <v>0.0004150854656472802</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004760982003062963</v>
+        <v>0.002196989255025983</v>
       </c>
       <c r="M18" t="n">
-        <v>0.004277616739273071</v>
+        <v>0.0001233181392308325</v>
       </c>
       <c r="N18" t="n">
-        <v>0.001392568228766322</v>
+        <v>0.0008736952440813184</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02339841984212399</v>
+        <v>0.002957521239295602</v>
       </c>
       <c r="P18" t="n">
-        <v>0.003282553981989622</v>
+        <v>0.0007229641196317971</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.005765826441347599</v>
+        <v>0.001141429995186627</v>
       </c>
       <c r="R18" t="n">
-        <v>0.003268550615757704</v>
+        <v>0.0007602698751725256</v>
       </c>
       <c r="S18" t="n">
-        <v>0.001115143299102783</v>
+        <v>0.0003698415530379862</v>
       </c>
       <c r="T18" t="n">
-        <v>3.761082189157605e-05</v>
+        <v>0.0002613832766655833</v>
       </c>
       <c r="U18" t="n">
-        <v>0.001077775610610843</v>
+        <v>0.0004894729354418814</v>
       </c>
       <c r="V18" t="n">
-        <v>0.004732299596071243</v>
+        <v>0.0003117910819128156</v>
       </c>
       <c r="W18" t="n">
-        <v>0.007069995161145926</v>
+        <v>0.0004383146297186613</v>
       </c>
       <c r="X18" t="n">
-        <v>0.003063063602894545</v>
+        <v>0.0003545150975696743</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.003728544106706977</v>
+        <v>0.0004746340273413807</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.001266673672944307</v>
+        <v>0.0001598483504494652</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.001574722584336996</v>
+        <v>0.0006517777219414711</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.0006820806302130222</v>
+        <v>0.001496051205322146</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.00299576111137867</v>
+        <v>0.0002462571137584746</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.004288997035473585</v>
+        <v>0.0004637493111658841</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.004184584598988295</v>
+        <v>0.0009825394954532385</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.005049087107181549</v>
+        <v>0.0005469632451422513</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.002218367531895638</v>
+        <v>0.0001455079182051122</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.003183268010616302</v>
+        <v>0.0004765074700117111</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.0004765181802213192</v>
+        <v>0.0003565481165423989</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.003232444869354367</v>
+        <v>0.0001076596454367973</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.003145259572193027</v>
+        <v>0.0003295844653621316</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.0009162595961242914</v>
+        <v>0.0002009563613682985</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.0008078385144472122</v>
+        <v>0.0002241286856587976</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.0005781529471278191</v>
+        <v>0.0002575996040832251</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.00232864054851234</v>
+        <v>0.0003525627544149756</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.005036280024796724</v>
+        <v>0.0003721348475664854</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.0006129165412858129</v>
+        <v>0.0003715376951731741</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.002513471757993102</v>
+        <v>0.0001290021318709478</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.001263864571228623</v>
+        <v>6.618455518037081e-05</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.002956627402454615</v>
+        <v>1.187305133498739e-05</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.01219525095075369</v>
+        <v>0.001334838685579598</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.0001581041142344475</v>
+        <v>0.0001830545515986159</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.009956154972314835</v>
+        <v>0.0001943319075508043</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.01375801209360361</v>
+        <v>4.757166607305408e-06</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.01696187816560268</v>
+        <v>0.00202161306515336</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.002535787178203464</v>
+        <v>0.0005480924155563116</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.002165734302252531</v>
+        <v>0.000375015486497432</v>
       </c>
       <c r="BB18" t="n">
-        <v>0.001563799567520618</v>
+        <v>0.0001091132508008741</v>
       </c>
       <c r="BC18" t="n">
-        <v>0.001426097005605698</v>
+        <v>0.001066639553755522</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.004336823709309101</v>
+        <v>0.0007783307810314</v>
       </c>
       <c r="BE18" t="n">
-        <v>0.006426420528441668</v>
+        <v>0.0009546051733195782</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.002668066415935755</v>
+        <v>0.0004978232318535447</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.0007530595175921917</v>
+        <v>0.0008002426475286484</v>
       </c>
       <c r="BH18" t="n">
-        <v>0.005297146271914244</v>
+        <v>6.320715328911319e-06</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.003838140051811934</v>
+        <v>7.111835293471813e-05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.001006116392090917</v>
+        <v>0.0004022276843897998</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.001285186503082514</v>
+        <v>0.001044355216436088</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.001705764327198267</v>
+        <v>4.305504262447357e-05</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.006985215470194817</v>
+        <v>0.0002401286910753697</v>
       </c>
       <c r="BN18" t="n">
-        <v>0.0002416030038148165</v>
+        <v>0.0009554261341691017</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.002895221579819918</v>
+        <v>1.791008980944753e-05</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.0001942283706739545</v>
+        <v>0.0002165808691643178</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.001308345585130155</v>
+        <v>0.0001655707019381225</v>
       </c>
       <c r="BR18" t="n">
-        <v>0.0005051849875599146</v>
+        <v>8.026519208215177e-05</v>
       </c>
       <c r="BS18" t="n">
-        <v>0.002171035390347242</v>
+        <v>6.058335202396847e-05</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.003928644116967916</v>
+        <v>0.0006292740581557155</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.001433730125427246</v>
+        <v>7.932468724902719e-05</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.006048678886145353</v>
+        <v>0.0004968275898136199</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.001850237604230642</v>
+        <v>0.0003228097048122436</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.006353255826979876</v>
+        <v>0.000425611186074093</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.006359624210745096</v>
+        <v>0.0001679986744420603</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.008787533268332481</v>
+        <v>0.001270261825993657</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.00346593651920557</v>
+        <v>9.811502968659624e-05</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.0002378404606133699</v>
+        <v>0.0001337564317509532</v>
       </c>
       <c r="CC18" t="n">
-        <v>0.0007467516115866601</v>
+        <v>0.0001978186191990972</v>
       </c>
       <c r="CD18" t="n">
-        <v>0.0002521783171687275</v>
+        <v>0.0003605991078075022</v>
       </c>
       <c r="CE18" t="n">
-        <v>0.002282569883391261</v>
+        <v>5.473013152368367e-05</v>
       </c>
       <c r="CF18" t="n">
-        <v>0.001794513431377709</v>
+        <v>0.0003760238760150969</v>
       </c>
       <c r="CG18" t="n">
-        <v>6.835168460384011e-05</v>
+        <v>0.0001467042457079515</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.001185364089906216</v>
+        <v>0.0001381922920700163</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.005927262362092733</v>
+        <v>0.0006017487030476332</v>
       </c>
       <c r="CJ18" t="n">
-        <v>0.0003924272605217993</v>
+        <v>0.0001142903493018821</v>
       </c>
       <c r="CK18" t="n">
-        <v>0.002752620726823807</v>
+        <v>0.0001574403722770512</v>
       </c>
       <c r="CL18" t="n">
-        <v>0.0002150882501155138</v>
+        <v>0.0003342972486279905</v>
       </c>
       <c r="CM18" t="n">
-        <v>0.00327482121065259</v>
+        <v>0.000187022946192883</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.001842703786678612</v>
+        <v>0.0002173652756027877</v>
       </c>
       <c r="CO18" t="n">
-        <v>0.0004825968353543431</v>
+        <v>0.000186614430276677</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.007068767212331295</v>
+        <v>0.0003018802381120622</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.00765291741117835</v>
+        <v>0.0007241608109325171</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.004196541383862495</v>
+        <v>0.0006184372468851507</v>
       </c>
       <c r="CS18" t="n">
-        <v>0.0007115944754332304</v>
+        <v>0.0003203429223503917</v>
       </c>
       <c r="CT18" t="n">
-        <v>0.003677323926240206</v>
+        <v>0.0005925658042542636</v>
       </c>
       <c r="CU18" t="n">
-        <v>0.0008257445879280567</v>
+        <v>6.137534364825115e-05</v>
       </c>
       <c r="CV18" t="n">
-        <v>0.00061989133246243</v>
+        <v>0.0003154943115077913</v>
       </c>
       <c r="CW18" t="n">
-        <v>0.001374547136947513</v>
+        <v>4.081095539731905e-05</v>
       </c>
       <c r="CX18" t="n">
-        <v>0.001761809806339443</v>
+        <v>0.0003678845532704145</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.001224629348143935</v>
+        <v>0.0001078520945156924</v>
       </c>
       <c r="CZ18" t="n">
-        <v>0.001123569905757904</v>
+        <v>0.0003367351309861988</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.006034443620592356</v>
+        <v>0.0006270637968555093</v>
       </c>
       <c r="DB18" t="n">
-        <v>0.0001659856643527746</v>
+        <v>0.0001006624079309404</v>
       </c>
       <c r="DC18" t="n">
-        <v>0.00291672395542264</v>
+        <v>0.0002921082195825875</v>
       </c>
       <c r="DD18" t="n">
-        <v>0.001248153508640826</v>
+        <v>0.0003016055561602116</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.001331204548478127</v>
+        <v>6.537063745781779e-05</v>
       </c>
       <c r="DF18" t="n">
-        <v>0.005969062447547913</v>
+        <v>6.163254147395492e-05</v>
       </c>
       <c r="DG18" t="n">
-        <v>0.0006720388773828745</v>
+        <v>0.0006295262137427926</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.01232828758656979</v>
+        <v>0.0005430240998975933</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.0008859573281370103</v>
+        <v>0.0001430328411515802</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.000681093311868608</v>
+        <v>0.0003475297125987709</v>
       </c>
       <c r="DK18" t="n">
-        <v>0.000109983142465353</v>
+        <v>0.0003295845817774534</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.005802537314593792</v>
+        <v>0.0006676657940261066</v>
       </c>
       <c r="DM18" t="n">
-        <v>0.001053106971085072</v>
+        <v>0.0006633700686506927</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.001524487277492881</v>
+        <v>0.0001730032963678241</v>
       </c>
       <c r="DO18" t="n">
-        <v>0.000367388129234314</v>
+        <v>0.0007415720028802752</v>
       </c>
       <c r="DP18" t="n">
-        <v>0.00262658903375268</v>
+        <v>9.07356443349272e-05</v>
       </c>
       <c r="DQ18" t="n">
-        <v>0.0007251966744661331</v>
+        <v>1.965226692846045e-05</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.001660295529291034</v>
+        <v>0.0009650260908529162</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.0008255766588263214</v>
+        <v>0.0003734971687663347</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.005557992495596409</v>
+        <v>0.0003492697142064571</v>
       </c>
       <c r="DU18" t="n">
-        <v>0.0002401021774858236</v>
+        <v>0.0001314558321610093</v>
       </c>
       <c r="DV18" t="n">
-        <v>0.00221957778558135</v>
+        <v>0.0005769581766799092</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.001176341320388019</v>
+        <v>2.042754567810334e-05</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.0008124150335788727</v>
+        <v>0.0003997824096586555</v>
       </c>
       <c r="DY18" t="n">
-        <v>0.00212203455157578</v>
+        <v>0.0004187401209492236</v>
       </c>
       <c r="DZ18" t="n">
-        <v>0.001768902293406427</v>
+        <v>0.0003140226181130856</v>
       </c>
       <c r="EA18" t="n">
-        <v>0.001726428396068513</v>
+        <v>0.0006087950896471739</v>
       </c>
       <c r="EB18" t="n">
-        <v>0.002879752079024911</v>
+        <v>0.0001060494905686937</v>
       </c>
       <c r="EC18" t="n">
-        <v>0.002156270667910576</v>
+        <v>0.0003729136369656771</v>
       </c>
       <c r="ED18" t="n">
-        <v>0.005558657459914684</v>
+        <v>0.0004828290257137269</v>
       </c>
       <c r="EE18" t="n">
-        <v>0.00102182780392468</v>
+        <v>0.0002449019229970872</v>
       </c>
       <c r="EF18" t="n">
-        <v>0.001225502346642315</v>
+        <v>3.679374640341848e-05</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.0008720722980797291</v>
+        <v>0.0003412050427868962</v>
       </c>
       <c r="EH18" t="n">
-        <v>0.001270994893275201</v>
+        <v>0.0001163313281722367</v>
       </c>
       <c r="EI18" t="n">
-        <v>0.0002237770822830498</v>
+        <v>0.0002503322903066874</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.001697758678346872</v>
+        <v>0.0005043385317549109</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.006208047270774841</v>
+        <v>0.0001475420867791399</v>
       </c>
       <c r="EL18" t="n">
-        <v>0.0002394774928689003</v>
+        <v>0.0002087803441099823</v>
       </c>
       <c r="EM18" t="n">
-        <v>0.001344852382317185</v>
+        <v>0.0001256768009625375</v>
       </c>
       <c r="EN18" t="n">
-        <v>0.0007835550932213664</v>
+        <v>0.0001881638454506174</v>
       </c>
       <c r="EO18" t="n">
-        <v>0.001614760374650359</v>
+        <v>0.000452429085271433</v>
       </c>
       <c r="EP18" t="n">
-        <v>0.0004826825461350381</v>
+        <v>0.0001718772109597921</v>
       </c>
       <c r="EQ18" t="n">
-        <v>0.001275302609428763</v>
+        <v>0.0002100007695844397</v>
       </c>
       <c r="ER18" t="n">
-        <v>0.0008481177501380444</v>
+        <v>0.0006258435314521194</v>
       </c>
       <c r="ES18" t="n">
-        <v>0.002289162948727608</v>
+        <v>0.0008006828720681369</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.001792618655599654</v>
+        <v>0.0009967496152967215</v>
       </c>
       <c r="EU18" t="n">
-        <v>0.001695735147222877</v>
+        <v>0.0007147707510739565</v>
       </c>
       <c r="EV18" t="n">
-        <v>0.005734649021178484</v>
+        <v>0.0002859267988242209</v>
       </c>
       <c r="EW18" t="n">
-        <v>0.003642867086455226</v>
+        <v>0.0001669427292654291</v>
       </c>
       <c r="EX18" t="n">
-        <v>0.0003665044787339866</v>
+        <v>0.0004126644053030759</v>
       </c>
       <c r="EY18" t="n">
-        <v>0.0005565616302192211</v>
+        <v>5.833410250488669e-05</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0.000627604138571769</v>
+        <v>0.0002651084214448929</v>
       </c>
       <c r="FA18" t="n">
-        <v>0.001076804124750197</v>
+        <v>6.841585854999721e-05</v>
       </c>
       <c r="FB18" t="n">
-        <v>0.001267751445993781</v>
+        <v>0.0001848655665526167</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.005184639245271683</v>
+        <v>0.0006117755547165871</v>
       </c>
       <c r="FD18" t="n">
-        <v>0.0003877496055793017</v>
+        <v>0.000147353668580763</v>
       </c>
       <c r="FE18" t="n">
-        <v>0.002316050697118044</v>
+        <v>6.252646562643349e-05</v>
       </c>
       <c r="FF18" t="n">
-        <v>0.0005810180446133018</v>
+        <v>0.0001962341775652021</v>
       </c>
       <c r="FG18" t="n">
-        <v>0.0008979382691904902</v>
+        <v>0.0002668563392944634</v>
       </c>
       <c r="FH18" t="n">
-        <v>0.002111537847667933</v>
+        <v>0.0001347613142570481</v>
       </c>
       <c r="FI18" t="n">
-        <v>0.000657210941426456</v>
+        <v>6.722184480167925e-05</v>
       </c>
       <c r="FJ18" t="n">
-        <v>0.0007349541992880404</v>
+        <v>0.000157647518790327</v>
       </c>
       <c r="FK18" t="n">
-        <v>0.002913238480687141</v>
+        <v>0.0003596364404074848</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.002934521064162254</v>
+        <v>0.0009816046804189682</v>
       </c>
       <c r="FM18" t="n">
-        <v>0.002188447862863541</v>
+        <v>0.0001078805871657096</v>
       </c>
       <c r="FN18" t="n">
-        <v>0.004390121903270483</v>
+        <v>0.000426213227910921</v>
       </c>
       <c r="FO18" t="n">
-        <v>0.001505593885667622</v>
+        <v>0.0006912964745424688</v>
       </c>
       <c r="FP18" t="n">
-        <v>0.003530498826876283</v>
+        <v>0.0005106034222990274</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.004228272940963507</v>
+        <v>0.0003293391782790422</v>
       </c>
       <c r="FR18" t="n">
-        <v>0.0007959630456753075</v>
+        <v>0.0002120270510204136</v>
       </c>
       <c r="FS18" t="n">
-        <v>0.002581775654107332</v>
+        <v>9.496106940787286e-06</v>
       </c>
       <c r="FT18" t="n">
-        <v>0.002000525593757629</v>
+        <v>0.001282748184166849</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.002193887252360582</v>
+        <v>0.000364799314411357</v>
       </c>
       <c r="FV18" t="n">
-        <v>0.001235633273608983</v>
+        <v>0.0003829074266832322</v>
       </c>
       <c r="FW18" t="n">
-        <v>0.005712625104933977</v>
+        <v>0.000147255981573835</v>
       </c>
       <c r="FX18" t="n">
-        <v>0.006055095698684454</v>
+        <v>0.001055671251378953</v>
       </c>
       <c r="FY18" t="n">
-        <v>0.003042407101020217</v>
+        <v>0.0004789375234395266</v>
       </c>
       <c r="FZ18" t="n">
-        <v>0.00248190457932651</v>
+        <v>0.0003233573806937784</v>
       </c>
       <c r="GA18" t="n">
-        <v>0.002742919838055968</v>
+        <v>0.0001775930431904271</v>
       </c>
       <c r="GB18" t="n">
-        <v>0.0001728893257677555</v>
+        <v>0.0004892769502475858</v>
       </c>
       <c r="GC18" t="n">
-        <v>0.01036663446575403</v>
+        <v>8.700029866304249e-05</v>
       </c>
       <c r="GD18" t="n">
-        <v>0.001607136800885201</v>
+        <v>0.0001153140474343672</v>
       </c>
       <c r="GE18" t="n">
-        <v>0.004987420979887247</v>
+        <v>0.000546042516361922</v>
       </c>
       <c r="GF18" t="n">
-        <v>2.486753510311246e-05</v>
+        <v>0.0005393092287704349</v>
       </c>
       <c r="GG18" t="n">
-        <v>0.0015468904748559</v>
+        <v>1.746160705806687e-06</v>
       </c>
     </row>
     <row r="19">
